--- a/統合版・2026年三陸鉄道周辺ダイヤ_4_2.xlsx
+++ b/統合版・2026年三陸鉄道周辺ダイヤ_4_2.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dnaka_cy7a7ax\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1F1B5C7-7380-4C32-BF55-84BE1496F7FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9894DE7A-FA51-4303-975B-15A8C399D855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16371" yWindow="0" windowWidth="14915" windowHeight="11709" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-    <workbookView xWindow="31114" yWindow="0" windowWidth="14915" windowHeight="11709" activeTab="2" xr2:uid="{3339B9FF-A08C-4853-B3B5-D870D1D967CF}"/>
+    <workbookView xWindow="30951" yWindow="326" windowWidth="7775" windowHeight="4405" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28517" yWindow="463" windowWidth="14683" windowHeight="10414" xr2:uid="{3339B9FF-A08C-4853-B3B5-D870D1D967CF}"/>
   </bookViews>
   <sheets>
     <sheet name="乗換設定" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2890" uniqueCount="1281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2900" uniqueCount="1281">
   <si>
     <t>事業者</t>
   </si>
@@ -4368,7 +4368,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="13.3" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.3046875" bestFit="1" customWidth="1"/>
@@ -4493,7 +4493,7 @@
         <v>14</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
         <v>42</v>
@@ -4513,7 +4513,7 @@
         <v>11</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
         <v>43</v>
@@ -4916,6 +4916,46 @@
         <v>10</v>
       </c>
       <c r="F27" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" t="s">
+        <v>10</v>
+      </c>
+      <c r="E28">
+        <v>10</v>
+      </c>
+      <c r="F28" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" t="s">
+        <v>7</v>
+      </c>
+      <c r="D29" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29">
+        <v>10</v>
+      </c>
+      <c r="F29" t="s">
         <v>1268</v>
       </c>
     </row>

--- a/統合版・2026年三陸鉄道周辺ダイヤ_4_2.xlsx
+++ b/統合版・2026年三陸鉄道周辺ダイヤ_4_2.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dnaka_cy7a7ax\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9894DE7A-FA51-4303-975B-15A8C399D855}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67125414-8784-4B4E-9F98-129A892C1E28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30951" yWindow="326" windowWidth="7775" windowHeight="4405" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-    <workbookView xWindow="28517" yWindow="463" windowWidth="14683" windowHeight="10414" xr2:uid="{3339B9FF-A08C-4853-B3B5-D870D1D967CF}"/>
+    <workbookView xWindow="16371" yWindow="0" windowWidth="14915" windowHeight="11709" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31114" yWindow="0" windowWidth="14915" windowHeight="11709" activeTab="2" xr2:uid="{3339B9FF-A08C-4853-B3B5-D870D1D967CF}"/>
   </bookViews>
   <sheets>
     <sheet name="乗換設定" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2900" uniqueCount="1281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2898" uniqueCount="1288">
   <si>
     <t>事業者</t>
   </si>
@@ -3963,6 +3963,51 @@
   <si>
     <t>施設→船着場</t>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>最寄り停留所</t>
+    <rPh sb="0" eb="2">
+      <t>モヨ</t>
+    </rPh>
+    <rPh sb="3" eb="6">
+      <t>テイリュウショ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>龍泉洞前</t>
+    <rPh sb="0" eb="4">
+      <t>リュウセンドウマエ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>出崎ふ頭</t>
+    <rPh sb="0" eb="2">
+      <t>デサキ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>トウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>浄土ヶ浜</t>
+    <rPh sb="0" eb="4">
+      <t>ジョウドガハマ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>宮古うみねこ丸（出崎ふ頭周遊）</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>宮古うみねこ丸（浄土ヶ浜周遊）</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>島越港</t>
   </si>
 </sst>
 </file>
@@ -4368,7 +4413,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr defaultRowHeight="13.3" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.3046875" bestFit="1" customWidth="1"/>
@@ -4524,99 +4569,99 @@
         <v>34</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="E8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C9" t="s">
         <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E9">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="B10" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="D10" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="E10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F10" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" t="s">
         <v>48</v>
       </c>
-      <c r="B11" t="s">
-        <v>22</v>
-      </c>
-      <c r="C11" t="s">
-        <v>34</v>
-      </c>
       <c r="D11" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="E11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F11" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="C12" t="s">
         <v>26</v>
       </c>
       <c r="D12" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E12">
         <v>3</v>
       </c>
       <c r="F12" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -4624,99 +4669,99 @@
         <v>26</v>
       </c>
       <c r="B13" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="E13">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B14" t="s">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="D14" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="E14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="B15" t="s">
-        <v>54</v>
+        <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="D15" t="s">
-        <v>53</v>
+        <v>9</v>
       </c>
       <c r="E15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D16" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>56</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C17" t="s">
         <v>12</v>
       </c>
-      <c r="B17" t="s">
-        <v>13</v>
-      </c>
-      <c r="C17" t="s">
-        <v>7</v>
-      </c>
       <c r="D17" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -4727,24 +4772,24 @@
         <v>14</v>
       </c>
       <c r="C18" t="s">
-        <v>7</v>
+        <v>1272</v>
       </c>
       <c r="D18" t="s">
-        <v>10</v>
+        <v>1277</v>
       </c>
       <c r="E18">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F18" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>7</v>
+        <v>1272</v>
       </c>
       <c r="B19" t="s">
-        <v>10</v>
+        <v>1277</v>
       </c>
       <c r="C19" t="s">
         <v>12</v>
@@ -4753,27 +4798,27 @@
         <v>14</v>
       </c>
       <c r="E19">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F19" t="s">
-        <v>58</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>1265</v>
+        <v>7</v>
       </c>
       <c r="B20" t="s">
-        <v>1264</v>
+        <v>11</v>
       </c>
       <c r="C20" t="s">
-        <v>17</v>
+        <v>1272</v>
       </c>
       <c r="D20" t="s">
-        <v>17</v>
+        <v>1277</v>
       </c>
       <c r="E20">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F20" t="s">
         <v>1267</v>
@@ -4781,19 +4826,19 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>17</v>
+        <v>1272</v>
       </c>
       <c r="B21" t="s">
-        <v>17</v>
+        <v>1277</v>
       </c>
       <c r="C21" t="s">
-        <v>1265</v>
+        <v>7</v>
       </c>
       <c r="D21" t="s">
-        <v>1264</v>
+        <v>11</v>
       </c>
       <c r="E21">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F21" t="s">
         <v>1268</v>
@@ -4801,10 +4846,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B22" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C22" t="s">
         <v>1272</v>
@@ -4813,10 +4858,10 @@
         <v>1277</v>
       </c>
       <c r="E22">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F22" t="s">
-        <v>1279</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -4827,16 +4872,16 @@
         <v>1277</v>
       </c>
       <c r="C23" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D23" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E23">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F23" t="s">
-        <v>1280</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -4847,13 +4892,13 @@
         <v>11</v>
       </c>
       <c r="C24" t="s">
-        <v>1272</v>
+        <v>7</v>
       </c>
       <c r="D24" t="s">
-        <v>1277</v>
+        <v>10</v>
       </c>
       <c r="E24">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F24" t="s">
         <v>1267</v>
@@ -4861,10 +4906,10 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1272</v>
+        <v>7</v>
       </c>
       <c r="B25" t="s">
-        <v>1277</v>
+        <v>10</v>
       </c>
       <c r="C25" t="s">
         <v>7</v>
@@ -4873,7 +4918,7 @@
         <v>11</v>
       </c>
       <c r="E25">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F25" t="s">
         <v>1268</v>
@@ -4881,82 +4926,42 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="B26" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="C26" t="s">
-        <v>1272</v>
+        <v>18</v>
       </c>
       <c r="D26" t="s">
-        <v>1277</v>
+        <v>1287</v>
       </c>
       <c r="E26">
         <v>10</v>
       </c>
       <c r="F26" t="s">
-        <v>1267</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1272</v>
+        <v>18</v>
       </c>
       <c r="B27" t="s">
-        <v>1277</v>
+        <v>1287</v>
       </c>
       <c r="C27" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="D27" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
       <c r="E27">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F27" t="s">
-        <v>1268</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>7</v>
-      </c>
-      <c r="B28" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" t="s">
-        <v>7</v>
-      </c>
-      <c r="D28" t="s">
-        <v>10</v>
-      </c>
-      <c r="E28">
-        <v>10</v>
-      </c>
-      <c r="F28" t="s">
-        <v>1267</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>7</v>
-      </c>
-      <c r="B29" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" t="s">
-        <v>7</v>
-      </c>
-      <c r="D29" t="s">
-        <v>11</v>
-      </c>
-      <c r="E29">
-        <v>10</v>
-      </c>
-      <c r="F29" t="s">
-        <v>1268</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -11992,87 +11997,120 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9E270AA-17A2-4D2C-AEFB-5A166D0C1BBB}">
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="13.3" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.07421875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.07421875" customWidth="1"/>
+    <col min="4" max="4" width="14.53515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1269</v>
       </c>
       <c r="B1" t="s">
+        <v>1281</v>
+      </c>
+      <c r="C1" t="s">
         <v>1270</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>1271</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>1275</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>17</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="s">
+        <v>1282</v>
+      </c>
+      <c r="C2">
         <v>1100</v>
       </c>
-      <c r="C2">
+      <c r="D2">
         <v>820</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3">
+        <v>1285</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C3">
         <v>1500</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>1350</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C4">
+        <v>1500</v>
+      </c>
+      <c r="D4">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>1272</v>
       </c>
-      <c r="B4">
+      <c r="B5" t="s">
+        <v>1277</v>
+      </c>
+      <c r="C5">
         <v>2000</v>
       </c>
-      <c r="C4">
+      <c r="D5">
         <v>2000</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>1273</v>
       </c>
-      <c r="B5">
+      <c r="B6" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C6">
         <v>2500</v>
       </c>
-      <c r="C5">
+      <c r="D6">
         <v>2250</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>19</v>
       </c>
-      <c r="B6">
+      <c r="B7" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C7">
         <v>3800</v>
       </c>
-      <c r="C6">
+      <c r="D7">
         <v>3800</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E7" t="s">
         <v>1276</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>1274</v>
       </c>
     </row>

--- a/統合版・2026年三陸鉄道周辺ダイヤ_4_2.xlsx
+++ b/統合版・2026年三陸鉄道周辺ダイヤ_4_2.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dnaka_cy7a7ax\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67125414-8784-4B4E-9F98-129A892C1E28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B99897D4-8B17-45DB-B225-53050767D098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16371" yWindow="0" windowWidth="14915" windowHeight="11709" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-    <workbookView xWindow="31114" yWindow="0" windowWidth="14915" windowHeight="11709" activeTab="2" xr2:uid="{3339B9FF-A08C-4853-B3B5-D870D1D967CF}"/>
+    <workbookView xWindow="31114" yWindow="0" windowWidth="14915" windowHeight="11709" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16371" yWindow="0" windowWidth="14915" windowHeight="11709" activeTab="1" xr2:uid="{3339B9FF-A08C-4853-B3B5-D870D1D967CF}"/>
   </bookViews>
   <sheets>
     <sheet name="乗換設定" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2898" uniqueCount="1288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2915" uniqueCount="1298">
   <si>
     <t>事業者</t>
   </si>
@@ -3992,22 +3992,107 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>浄土ヶ浜</t>
+    <t>宮古うみねこ丸（出崎ふ頭周遊）</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>宮古うみねこ丸（浄土ヶ浜周遊）</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>島越港</t>
+  </si>
+  <si>
+    <t>岩泉町民バス</t>
     <rPh sb="0" eb="4">
+      <t>イワイズミチョウミン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>岩手県北バス</t>
+    <rPh sb="0" eb="4">
+      <t>イワテケンポク</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>宮古うみねこ丸・浄土ヶ浜</t>
+    <rPh sb="0" eb="2">
+      <t>ミヤコ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>マル</t>
+    </rPh>
+    <rPh sb="8" eb="12">
       <t>ジョウドガハマ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>宮古うみねこ丸（出崎ふ頭周遊）</t>
+    <t>宮古うみねこ丸</t>
+    <rPh sb="0" eb="2">
+      <t>ミヤコ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>マル</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>宮古うみねこ丸（浄土ヶ浜周遊）</t>
+    <t>最寄り交通機関</t>
+    <rPh sb="0" eb="2">
+      <t>モヨ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>コウツウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>キカン</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>島越港</t>
+    <t>奥浄土ヶ浜</t>
+    <rPh sb="0" eb="5">
+      <t>オクジョウドガハマ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>宮古市内観光</t>
+    <rPh sb="0" eb="4">
+      <t>ミヤコシナイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カンコウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>宮古駅前</t>
+    <rPh sb="0" eb="4">
+      <t>ミヤコエキマエ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>北山崎展望台</t>
+    <rPh sb="3" eb="6">
+      <t>テンボウダイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>北山崎</t>
+    <rPh sb="0" eb="3">
+      <t>キタヤマザキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ＪＲバス</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -4417,9 +4502,9 @@
   <sheetFormatPr defaultRowHeight="13.3" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.3046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.69140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.15234375" customWidth="1"/>
     <col min="3" max="3" width="19.3046875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.69140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23" customWidth="1"/>
     <col min="5" max="5" width="13.4609375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.84375" bestFit="1" customWidth="1"/>
   </cols>
@@ -4449,13 +4534,13 @@
         <v>34</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>1262</v>
+        <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="E2">
         <v>5</v>
@@ -4466,16 +4551,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1265</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C3" t="s">
         <v>34</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E3">
         <v>10</v>
@@ -4486,62 +4571,62 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>1289</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C5" t="s">
         <v>7</v>
       </c>
-      <c r="B5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C5" t="s">
-        <v>34</v>
-      </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
         <v>12</v>
       </c>
       <c r="D6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -4549,187 +4634,187 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C7" t="s">
         <v>7</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>47</v>
+        <v>1289</v>
       </c>
       <c r="C8" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>49</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
+        <v>1289</v>
       </c>
       <c r="E9">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>1289</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>1272</v>
       </c>
       <c r="D10" t="s">
-        <v>51</v>
+        <v>1277</v>
       </c>
       <c r="E10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>52</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>1272</v>
       </c>
       <c r="B11" t="s">
-        <v>51</v>
+        <v>1277</v>
       </c>
       <c r="C11" t="s">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="D11" t="s">
-        <v>23</v>
+        <v>1289</v>
       </c>
       <c r="E11">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>52</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>26</v>
+        <v>1272</v>
       </c>
       <c r="D12" t="s">
-        <v>54</v>
+        <v>1277</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>55</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>1272</v>
       </c>
       <c r="B13" t="s">
-        <v>54</v>
+        <v>1277</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="D13" t="s">
-        <v>53</v>
+        <v>11</v>
       </c>
       <c r="E13">
         <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>38</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>1272</v>
       </c>
       <c r="D14" t="s">
-        <v>13</v>
+        <v>1277</v>
       </c>
       <c r="E14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>56</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>1272</v>
       </c>
       <c r="B15" t="s">
-        <v>13</v>
+        <v>1277</v>
       </c>
       <c r="C15" t="s">
         <v>7</v>
       </c>
       <c r="D15" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>57</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B16" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C16" t="s">
         <v>7</v>
@@ -4738,10 +4823,10 @@
         <v>10</v>
       </c>
       <c r="E16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>1278</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -4752,176 +4837,176 @@
         <v>10</v>
       </c>
       <c r="C17" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D17" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>58</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="B18" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>1272</v>
+        <v>1262</v>
       </c>
       <c r="D18" t="s">
-        <v>1277</v>
+        <v>36</v>
       </c>
       <c r="E18">
         <v>5</v>
       </c>
       <c r="F18" t="s">
-        <v>1279</v>
+        <v>37</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1272</v>
+        <v>1265</v>
       </c>
       <c r="B19" t="s">
-        <v>1277</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="D19" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="E19">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F19" t="s">
-        <v>1280</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="B20" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="C20" t="s">
-        <v>1272</v>
+        <v>48</v>
       </c>
       <c r="D20" t="s">
-        <v>1277</v>
+        <v>22</v>
       </c>
       <c r="E20">
         <v>5</v>
       </c>
       <c r="F20" t="s">
-        <v>1267</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1272</v>
+        <v>48</v>
       </c>
       <c r="B21" t="s">
-        <v>1277</v>
+        <v>22</v>
       </c>
       <c r="C21" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="D21" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="E21">
         <v>5</v>
       </c>
       <c r="F21" t="s">
-        <v>1268</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="B22" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="C22" t="s">
-        <v>1272</v>
+        <v>26</v>
       </c>
       <c r="D22" t="s">
-        <v>1277</v>
+        <v>51</v>
       </c>
       <c r="E22">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F22" t="s">
-        <v>1267</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1272</v>
+        <v>26</v>
       </c>
       <c r="B23" t="s">
-        <v>1277</v>
+        <v>51</v>
       </c>
       <c r="C23" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="D23" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E23">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F23" t="s">
-        <v>1268</v>
+        <v>52</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="B24" t="s">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="C24" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="D24" t="s">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="E24">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F24" t="s">
-        <v>1267</v>
+        <v>55</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="B25" t="s">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="C25" t="s">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="D25" t="s">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="E25">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F25" t="s">
-        <v>1268</v>
+        <v>38</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -4935,7 +5020,7 @@
         <v>18</v>
       </c>
       <c r="D26" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="E26">
         <v>10</v>
@@ -4949,7 +5034,7 @@
         <v>18</v>
       </c>
       <c r="B27" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="C27" t="s">
         <v>34</v>
@@ -11997,121 +12082,196 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9E270AA-17A2-4D2C-AEFB-5A166D0C1BBB}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="13.3" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.07421875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.07421875" customWidth="1"/>
-    <col min="4" max="4" width="14.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="30.07421875" customWidth="1"/>
+    <col min="5" max="5" width="14.53515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>1269</v>
       </c>
       <c r="B1" t="s">
+        <v>1291</v>
+      </c>
+      <c r="C1" t="s">
         <v>1281</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>1270</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>1271</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>1275</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>1292</v>
       </c>
       <c r="B2" t="s">
-        <v>1282</v>
-      </c>
-      <c r="C2">
-        <v>1100</v>
+        <v>1288</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1292</v>
       </c>
       <c r="D2">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1283</v>
+      </c>
+      <c r="D3">
+        <v>1500</v>
+      </c>
+      <c r="E3">
+        <v>1350</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>1285</v>
       </c>
-      <c r="B3" t="s">
-        <v>1283</v>
-      </c>
-      <c r="C3">
+      <c r="B4" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1289</v>
+      </c>
+      <c r="D4">
         <v>1500</v>
       </c>
-      <c r="D3">
+      <c r="E4">
         <v>1350</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>1286</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1284</v>
-      </c>
-      <c r="C4">
-        <v>1500</v>
-      </c>
-      <c r="D4">
-        <v>1350</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1272</v>
       </c>
       <c r="B5" t="s">
+        <v>1272</v>
+      </c>
+      <c r="C5" t="s">
         <v>1277</v>
-      </c>
-      <c r="C5">
-        <v>2000</v>
       </c>
       <c r="D5">
         <v>2000</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E5">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1288</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1294</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1282</v>
+      </c>
+      <c r="D7">
+        <v>1100</v>
+      </c>
+      <c r="E7">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>1273</v>
       </c>
-      <c r="B6" t="s">
-        <v>1287</v>
-      </c>
-      <c r="C6">
+      <c r="B8" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1286</v>
+      </c>
+      <c r="D8">
         <v>2500</v>
       </c>
-      <c r="D6">
+      <c r="E8">
         <v>2250</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>19</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" t="s">
         <v>1176</v>
       </c>
-      <c r="C7">
+      <c r="D9">
         <v>3800</v>
       </c>
-      <c r="D7">
+      <c r="E9">
         <v>3800</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F9" t="s">
         <v>1276</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1296</v>
+      </c>
+      <c r="D10">
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>1274</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1297</v>
       </c>
     </row>
   </sheetData>

--- a/統合版・2026年三陸鉄道周辺ダイヤ_4_2.xlsx
+++ b/統合版・2026年三陸鉄道周辺ダイヤ_4_2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dnaka_cy7a7ax\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B99897D4-8B17-45DB-B225-53050767D098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E56D0D87-08F7-4DB0-9F68-93372493ABAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31114" yWindow="0" windowWidth="14915" windowHeight="11709" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31114" yWindow="0" windowWidth="14915" windowHeight="11709" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
     <workbookView xWindow="16371" yWindow="0" windowWidth="14915" windowHeight="11709" activeTab="1" xr2:uid="{3339B9FF-A08C-4853-B3B5-D870D1D967CF}"/>
   </bookViews>
   <sheets>
@@ -21,7 +21,7 @@
     <sheet name="三陸鉄道_南行" sheetId="3" r:id="rId5"/>
     <sheet name="岩泉町民バス_西行" sheetId="4" r:id="rId6"/>
     <sheet name="岩泉町民バス_東行" sheetId="5" r:id="rId7"/>
-    <sheet name="岩泉町民バス_往路" sheetId="6" r:id="rId8"/>
+    <sheet name="岩手県北バス_往路" sheetId="6" r:id="rId8"/>
     <sheet name="岩手県北バス_復路" sheetId="7" r:id="rId9"/>
     <sheet name="宮古うみねこ丸便" sheetId="8" r:id="rId10"/>
     <sheet name="北山崎断崖クルーズ" sheetId="9" r:id="rId11"/>

--- a/統合版・2026年三陸鉄道周辺ダイヤ_4_2.xlsx
+++ b/統合版・2026年三陸鉄道周辺ダイヤ_4_2.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dnaka_cy7a7ax\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DB177E9-B222-419B-8403-E9A831824744}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9870BC9-EB91-47CA-8B05-630A58012C32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31114" yWindow="0" windowWidth="14915" windowHeight="11709" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-    <workbookView xWindow="16371" yWindow="0" windowWidth="14915" windowHeight="11709" xr2:uid="{3339B9FF-A08C-4853-B3B5-D870D1D967CF}"/>
+    <workbookView xWindow="31114" yWindow="0" windowWidth="14915" windowHeight="11709" firstSheet="7" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="29314" yWindow="463" windowWidth="4697" windowHeight="9651" xr2:uid="{3339B9FF-A08C-4853-B3B5-D870D1D967CF}"/>
   </bookViews>
   <sheets>
     <sheet name="乗換設定" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2930" uniqueCount="1303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2930" uniqueCount="1301">
   <si>
     <t>事業者</t>
   </si>
@@ -3472,12 +3472,6 @@
   </si>
   <si>
     <t>出崎ふ頭_発</t>
-  </si>
-  <si>
-    <t>浄土ヶ浜_着</t>
-  </si>
-  <si>
-    <t>浄土ヶ浜_発</t>
   </si>
   <si>
     <t>出崎ふ頭_着</t>
@@ -4622,7 +4616,7 @@
         <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="E4">
         <v>8</v>
@@ -4636,7 +4630,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="C5" t="s">
         <v>7</v>
@@ -4696,7 +4690,7 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="C8" t="s">
         <v>7</v>
@@ -4708,7 +4702,7 @@
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -4722,7 +4716,7 @@
         <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -4736,39 +4730,39 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="C10" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="D10" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="E10">
         <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="B11" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="C11" t="s">
         <v>12</v>
       </c>
       <c r="D11" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="E11">
         <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -4779,24 +4773,24 @@
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="D12" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="E12">
         <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="B13" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="C13" t="s">
         <v>7</v>
@@ -4808,7 +4802,7 @@
         <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -4819,24 +4813,24 @@
         <v>10</v>
       </c>
       <c r="C14" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="D14" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="E14">
         <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="B15" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="C15" t="s">
         <v>7</v>
@@ -4848,7 +4842,7 @@
         <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -4868,7 +4862,7 @@
         <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -4888,7 +4882,7 @@
         <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -4899,7 +4893,7 @@
         <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="D18" t="s">
         <v>36</v>
@@ -4913,7 +4907,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="B19" t="s">
         <v>36</v>
@@ -5062,7 +5056,7 @@
         <v>18</v>
       </c>
       <c r="D26" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="E26">
         <v>10</v>
@@ -5076,7 +5070,7 @@
         <v>18</v>
       </c>
       <c r="B27" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="C27" t="s">
         <v>34</v>
@@ -5131,27 +5125,27 @@
         <v>1140</v>
       </c>
       <c r="I1" t="s">
+        <v>1286</v>
+      </c>
+      <c r="J1" t="s">
+        <v>1286</v>
+      </c>
+      <c r="K1" t="s">
         <v>1141</v>
-      </c>
-      <c r="J1" t="s">
-        <v>1142</v>
-      </c>
-      <c r="K1" t="s">
-        <v>1143</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="B2" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="C2" t="s">
         <v>147</v>
       </c>
       <c r="F2" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="H2" s="2">
         <v>0.375</v>
@@ -5168,16 +5162,16 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="B3" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="C3" t="s">
         <v>147</v>
       </c>
       <c r="F3" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="H3" s="2">
         <v>0.4236111111111111</v>
@@ -5194,16 +5188,16 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="B4" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="C4" t="s">
         <v>147</v>
       </c>
       <c r="F4" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="H4" s="2">
         <v>0.46527777777777779</v>
@@ -5220,16 +5214,16 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="B5" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="C5" t="s">
         <v>147</v>
       </c>
       <c r="F5" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="H5" s="2">
         <v>0.54861111111111116</v>
@@ -5246,16 +5240,16 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="B6" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="C6" t="s">
         <v>147</v>
       </c>
       <c r="F6" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="H6" s="2">
         <v>0.59027777777777779</v>
@@ -5272,16 +5266,16 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="B7" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="C7" t="s">
         <v>147</v>
       </c>
       <c r="F7" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="H7" s="2">
         <v>0.63194444444444442</v>
@@ -5298,16 +5292,16 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="B8" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="C8" t="s">
         <v>147</v>
       </c>
       <c r="F8" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="H8" s="2">
         <v>0.67361111111111116</v>
@@ -5361,18 +5355,18 @@
         <v>64</v>
       </c>
       <c r="H1" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="I1" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="B2" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="C2" t="s">
         <v>147</v>
@@ -5386,10 +5380,10 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="B3" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="C3" t="s">
         <v>147</v>
@@ -5403,19 +5397,19 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1164</v>
+      </c>
+      <c r="C4" t="s">
         <v>1165</v>
       </c>
-      <c r="B4" t="s">
+      <c r="F4" t="s">
         <v>1166</v>
       </c>
-      <c r="C4" t="s">
+      <c r="G4" t="s">
         <v>1167</v>
-      </c>
-      <c r="F4" t="s">
-        <v>1168</v>
-      </c>
-      <c r="G4" t="s">
-        <v>1169</v>
       </c>
       <c r="H4" s="2">
         <v>0.5</v>
@@ -5426,10 +5420,10 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="B5" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="C5" t="s">
         <v>147</v>
@@ -5443,19 +5437,19 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="B6" t="s">
-        <v>1172</v>
+        <v>1170</v>
       </c>
       <c r="C6" t="s">
+        <v>1165</v>
+      </c>
+      <c r="F6" t="s">
+        <v>1166</v>
+      </c>
+      <c r="G6" t="s">
         <v>1167</v>
-      </c>
-      <c r="F6" t="s">
-        <v>1168</v>
-      </c>
-      <c r="G6" t="s">
-        <v>1169</v>
       </c>
       <c r="H6" s="2">
         <v>0.60416666666666663</v>
@@ -5466,10 +5460,10 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="B7" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="C7" t="s">
         <v>147</v>
@@ -5515,21 +5509,21 @@
         <v>64</v>
       </c>
       <c r="H1" t="s">
+        <v>1172</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1173</v>
+      </c>
+      <c r="J1" t="s">
         <v>1174</v>
-      </c>
-      <c r="I1" t="s">
-        <v>1175</v>
-      </c>
-      <c r="J1" t="s">
-        <v>1176</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="B2" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="C2" t="s">
         <v>147</v>
@@ -5546,10 +5540,10 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="B3" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="C3" t="s">
         <v>147</v>
@@ -5566,10 +5560,10 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="B4" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="C4" t="s">
         <v>147</v>
@@ -5586,10 +5580,10 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="B5" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="C5" t="s">
         <v>147</v>
@@ -5606,10 +5600,10 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="B6" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="C6" t="s">
         <v>147</v>
@@ -5626,10 +5620,10 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="B7" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C7" t="s">
         <v>147</v>
@@ -5678,21 +5672,21 @@
         <v>64</v>
       </c>
       <c r="H1" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="I1" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="J1" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="B2" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="C2" t="s">
         <v>147</v>
@@ -5709,10 +5703,10 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="B3" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="C3" t="s">
         <v>147</v>
@@ -5729,10 +5723,10 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="B4" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="C4" t="s">
         <v>147</v>
@@ -5749,10 +5743,10 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="B5" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="C5" t="s">
         <v>147</v>
@@ -5769,10 +5763,10 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="B6" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="C6" t="s">
         <v>147</v>
@@ -5789,10 +5783,10 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="B7" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
       <c r="C7" t="s">
         <v>147</v>
@@ -5844,43 +5838,43 @@
         <v>53</v>
       </c>
       <c r="I1" t="s">
+        <v>1195</v>
+      </c>
+      <c r="J1" t="s">
+        <v>1196</v>
+      </c>
+      <c r="K1" t="s">
         <v>1197</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>1198</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>1199</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>1200</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>1201</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>1202</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>1203</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>1204</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>1205</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>1206</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>1207</v>
-      </c>
-      <c r="T1" t="s">
-        <v>1208</v>
-      </c>
-      <c r="U1" t="s">
-        <v>1209</v>
       </c>
       <c r="V1" t="s">
         <v>50</v>
@@ -5888,10 +5882,10 @@
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="B2" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="C2" t="s">
         <v>147</v>
@@ -5905,10 +5899,10 @@
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="B3" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="C3" t="s">
         <v>147</v>
@@ -5940,10 +5934,10 @@
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="B4" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="C4" t="s">
         <v>147</v>
@@ -5993,10 +5987,10 @@
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="B5" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="C5" t="s">
         <v>147</v>
@@ -6046,10 +6040,10 @@
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="B6" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="C6" t="s">
         <v>147</v>
@@ -6125,43 +6119,43 @@
         <v>50</v>
       </c>
       <c r="I1" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="J1" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="K1" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="L1" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="M1" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="N1" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="O1" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="P1" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="Q1" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="R1" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="S1" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="T1" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="U1" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="V1" t="s">
         <v>53</v>
@@ -6169,10 +6163,10 @@
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="B2" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="C2" t="s">
         <v>147</v>
@@ -6213,10 +6207,10 @@
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="B3" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="C3" t="s">
         <v>147</v>
@@ -6260,10 +6254,10 @@
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="B4" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="C4" t="s">
         <v>147</v>
@@ -6313,10 +6307,10 @@
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="B5" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="C5" t="s">
         <v>147</v>
@@ -6366,10 +6360,10 @@
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="B6" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="C6" t="s">
         <v>147</v>
@@ -6421,94 +6415,94 @@
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="B1" s="3" t="s">
+        <v>1223</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1224</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>1225</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>1226</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>1227</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>1228</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>1229</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>1230</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>1231</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>1232</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>1233</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>1234</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>1235</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>1236</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>1237</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>1238</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>1239</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>1240</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>1241</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>1242</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>1243</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>1244</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>1245</v>
-      </c>
-      <c r="W1" s="3" t="s">
-        <v>1246</v>
-      </c>
-      <c r="X1" s="3" t="s">
-        <v>1247</v>
       </c>
       <c r="Y1" s="3" t="s">
         <v>39</v>
       </c>
       <c r="Z1" s="3" t="s">
+        <v>1246</v>
+      </c>
+      <c r="AA1" s="3" t="s">
+        <v>1247</v>
+      </c>
+      <c r="AB1" s="3" t="s">
         <v>1248</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AC1" s="3" t="s">
         <v>1249</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AD1" s="3" t="s">
         <v>1250</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AE1" s="3" t="s">
         <v>1251</v>
-      </c>
-      <c r="AD1" s="3" t="s">
-        <v>1252</v>
-      </c>
-      <c r="AE1" s="3" t="s">
-        <v>1253</v>
       </c>
       <c r="AF1" s="3" t="s">
         <v>35</v>
@@ -6523,30 +6517,30 @@
         <v>52</v>
       </c>
       <c r="AJ1" s="3" t="s">
+        <v>1252</v>
+      </c>
+      <c r="AK1" s="3" t="s">
+        <v>1253</v>
+      </c>
+      <c r="AL1" s="3" t="s">
         <v>1254</v>
       </c>
-      <c r="AK1" s="3" t="s">
+      <c r="AM1" s="3" t="s">
         <v>1255</v>
       </c>
-      <c r="AL1" s="3" t="s">
+      <c r="AN1" s="3" t="s">
         <v>1256</v>
       </c>
-      <c r="AM1" s="3" t="s">
+      <c r="AO1" s="3" t="s">
         <v>1257</v>
       </c>
-      <c r="AN1" s="3" t="s">
+      <c r="AP1" s="3" t="s">
         <v>1258</v>
-      </c>
-      <c r="AO1" s="3" t="s">
-        <v>1259</v>
-      </c>
-      <c r="AP1" s="3" t="s">
-        <v>1260</v>
       </c>
     </row>
     <row r="2" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -6674,7 +6668,7 @@
     </row>
     <row r="3" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="B3">
         <v>290</v>
@@ -6802,7 +6796,7 @@
     </row>
     <row r="4" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="B4">
         <v>440</v>
@@ -6930,7 +6924,7 @@
     </row>
     <row r="5" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="B5">
         <v>440</v>
@@ -7058,7 +7052,7 @@
     </row>
     <row r="6" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="B6">
         <v>510</v>
@@ -7186,7 +7180,7 @@
     </row>
     <row r="7" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="B7">
         <v>610</v>
@@ -7314,7 +7308,7 @@
     </row>
     <row r="8" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="B8">
         <v>790</v>
@@ -7442,7 +7436,7 @@
     </row>
     <row r="9" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="B9">
         <v>940</v>
@@ -7570,7 +7564,7 @@
     </row>
     <row r="10" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="B10">
         <v>1120</v>
@@ -7698,7 +7692,7 @@
     </row>
     <row r="11" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="B11">
         <v>1210</v>
@@ -7826,7 +7820,7 @@
     </row>
     <row r="12" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="B12">
         <v>1370</v>
@@ -7954,7 +7948,7 @@
     </row>
     <row r="13" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="B13">
         <v>1370</v>
@@ -8082,7 +8076,7 @@
     </row>
     <row r="14" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="B14">
         <v>1510</v>
@@ -8210,7 +8204,7 @@
     </row>
     <row r="15" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="B15">
         <v>1600</v>
@@ -8338,7 +8332,7 @@
     </row>
     <row r="16" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="B16">
         <v>1700</v>
@@ -8466,7 +8460,7 @@
     </row>
     <row r="17" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
       <c r="B17">
         <v>1860</v>
@@ -8594,7 +8588,7 @@
     </row>
     <row r="18" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
       <c r="B18">
         <v>1940</v>
@@ -8722,7 +8716,7 @@
     </row>
     <row r="19" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="B19">
         <v>1940</v>
@@ -8850,7 +8844,7 @@
     </row>
     <row r="20" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="B20">
         <v>2220</v>
@@ -8978,7 +8972,7 @@
     </row>
     <row r="21" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="B21">
         <v>2280</v>
@@ -9106,7 +9100,7 @@
     </row>
     <row r="22" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="B22">
         <v>2350</v>
@@ -9234,7 +9228,7 @@
     </row>
     <row r="23" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B23">
         <v>2480</v>
@@ -9362,7 +9356,7 @@
     </row>
     <row r="24" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="B24">
         <v>2480</v>
@@ -9618,7 +9612,7 @@
     </row>
     <row r="26" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="B26">
         <v>2610</v>
@@ -9746,7 +9740,7 @@
     </row>
     <row r="27" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
       <c r="B27">
         <v>2680</v>
@@ -9874,7 +9868,7 @@
     </row>
     <row r="28" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
       <c r="B28">
         <v>2750</v>
@@ -10002,7 +9996,7 @@
     </row>
     <row r="29" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="B29">
         <v>2820</v>
@@ -10130,7 +10124,7 @@
     </row>
     <row r="30" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="B30">
         <v>2890</v>
@@ -10258,7 +10252,7 @@
     </row>
     <row r="31" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="B31">
         <v>3020</v>
@@ -10898,7 +10892,7 @@
     </row>
     <row r="36" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="B36">
         <v>3620</v>
@@ -11026,7 +11020,7 @@
     </row>
     <row r="37" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="B37">
         <v>3690</v>
@@ -11154,7 +11148,7 @@
     </row>
     <row r="38" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="B38">
         <v>3820</v>
@@ -11282,7 +11276,7 @@
     </row>
     <row r="39" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="B39">
         <v>3820</v>
@@ -11410,7 +11404,7 @@
     </row>
     <row r="40" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="B40">
         <v>3890</v>
@@ -11538,7 +11532,7 @@
     </row>
     <row r="41" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="B41">
         <v>3960</v>
@@ -11666,7 +11660,7 @@
     </row>
     <row r="42" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="B42">
         <v>4160</v>
@@ -12016,16 +12010,16 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1263</v>
+      </c>
+      <c r="D12" t="s">
         <v>1261</v>
-      </c>
-      <c r="B12" t="s">
-        <v>1262</v>
-      </c>
-      <c r="C12" t="s">
-        <v>1265</v>
-      </c>
-      <c r="D12" t="s">
-        <v>1263</v>
       </c>
       <c r="E12">
         <v>620</v>
@@ -12135,39 +12129,39 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="B1" t="s">
+        <v>1266</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1288</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1278</v>
+      </c>
+      <c r="E1" t="s">
+        <v>1267</v>
+      </c>
+      <c r="F1" t="s">
         <v>1268</v>
       </c>
-      <c r="C1" t="s">
-        <v>1290</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1280</v>
-      </c>
-      <c r="E1" t="s">
-        <v>1269</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1270</v>
-      </c>
       <c r="G1" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="B2" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="C2" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="D2" t="s">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -12178,16 +12172,16 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="B3" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="C3" t="s">
-        <v>1287</v>
+        <v>1285</v>
       </c>
       <c r="D3" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="E3">
         <v>1500</v>
@@ -12198,16 +12192,16 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="B4" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="C4" t="s">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="D4" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="E4">
         <v>1500</v>
@@ -12218,16 +12212,16 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="B5" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="C5" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="D5" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="E5">
         <v>2000</v>
@@ -12238,16 +12232,16 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="B6" t="s">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="C6" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
       <c r="D6" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -12258,16 +12252,16 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="B7" t="s">
         <v>17</v>
       </c>
       <c r="C7" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
       <c r="D7" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="E7">
         <v>1100</v>
@@ -12278,16 +12272,16 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="B8" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="C8" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="D8" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="E8">
         <v>2500</v>
@@ -12298,7 +12292,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="B9" t="s">
         <v>19</v>
@@ -12307,7 +12301,7 @@
         <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="E9">
         <v>3800</v>
@@ -12316,21 +12310,21 @@
         <v>3800</v>
       </c>
       <c r="G9" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="B10" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="C10" t="s">
         <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -12341,27 +12335,27 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="B11" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="C11" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="B12" t="s">
+        <v>1294</v>
+      </c>
+      <c r="C12" t="s">
         <v>1296</v>
       </c>
-      <c r="C12" t="s">
-        <v>1298</v>
-      </c>
       <c r="D12" t="s">
-        <v>1299</v>
+        <v>1297</v>
       </c>
       <c r="E12">
         <v>0</v>

--- a/統合版・2026年三陸鉄道周辺ダイヤ_4_2.xlsx
+++ b/統合版・2026年三陸鉄道周辺ダイヤ_4_2.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dnaka_cy7a7ax\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9870BC9-EB91-47CA-8B05-630A58012C32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65043FBE-794C-4FF0-80C2-F84AA7F23242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31114" yWindow="0" windowWidth="14915" windowHeight="11709" firstSheet="7" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-    <workbookView minimized="1" xWindow="29314" yWindow="463" windowWidth="4697" windowHeight="9651" xr2:uid="{3339B9FF-A08C-4853-B3B5-D870D1D967CF}"/>
+    <workbookView xWindow="31114" yWindow="0" windowWidth="14915" windowHeight="11709" activeTab="2" xr2:uid="{3339B9FF-A08C-4853-B3B5-D870D1D967CF}"/>
+    <workbookView xWindow="16354" yWindow="-103" windowWidth="29692" windowHeight="11829" firstSheet="1" activeTab="2" xr2:uid="{EECD383A-838A-41CD-8AB1-343EAFF88011}"/>
   </bookViews>
   <sheets>
     <sheet name="乗換設定" sheetId="1" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2930" uniqueCount="1301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2951" uniqueCount="1313">
   <si>
     <t>事業者</t>
   </si>
@@ -3469,12 +3469,6 @@
   </si>
   <si>
     <t>JOD_HI09</t>
-  </si>
-  <si>
-    <t>出崎ふ頭_発</t>
-  </si>
-  <si>
-    <t>出崎ふ頭_着</t>
   </si>
   <si>
     <t>UMI_01</t>
@@ -3973,24 +3967,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>出崎ふ頭</t>
-    <rPh sb="0" eb="2">
-      <t>デサキ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>トウ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>宮古うみねこ丸（出崎ふ頭周遊）</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>宮古うみねこ丸（浄土ヶ浜周遊）</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>島越港</t>
   </si>
   <si>
@@ -4006,6 +3982,9 @@
       <t>イワテケンポク</t>
     </rPh>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>宮古うみねこ丸・浄土ヶ浜</t>
   </si>
   <si>
     <t>宮古うみねこ丸・浄土ヶ浜</t>
@@ -4021,16 +4000,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>宮古うみねこ丸</t>
-    <rPh sb="0" eb="2">
-      <t>ミヤコ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>マル</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>最寄り交通機関</t>
     <rPh sb="0" eb="2">
       <t>モヨ</t>
@@ -4129,6 +4098,84 @@
       <t>タノハタ</t>
     </rPh>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>島越</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>所要時間固定</t>
+  </si>
+  <si>
+    <t>所要時間</t>
+  </si>
+  <si>
+    <t>可変</t>
+  </si>
+  <si>
+    <t>固定</t>
+  </si>
+  <si>
+    <t>固定</t>
+    <rPh sb="0" eb="2">
+      <t>コテイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>出崎ふ頭_着</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>宮古うみねこ丸・浄土ヶ浜_着</t>
+    <rPh sb="0" eb="2">
+      <t>ミヤコ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>マル</t>
+    </rPh>
+    <rPh sb="8" eb="12">
+      <t>ジョウドガハマ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>出崎ふ頭_発</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>宮古うみねこ丸・浄土ヶ浜_発</t>
+    <rPh sb="0" eb="2">
+      <t>ミヤコ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>マル</t>
+    </rPh>
+    <rPh sb="8" eb="12">
+      <t>ジョウドガハマ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>宮古うみねこ丸便</t>
+  </si>
+  <si>
+    <t>宮古うみねこ丸（片道移動）</t>
+  </si>
+  <si>
+    <t>宮古うみねこ丸（湾内周遊＋移動）</t>
+  </si>
+  <si>
+    <t>出崎ふ頭発⇒湾内周遊⇒浄土ヶ浜下船</t>
+  </si>
+  <si>
+    <t>出崎ふ頭・浄土ヶ浜間のショートカット</t>
+  </si>
+  <si>
+    <t>宮古うみねこ丸（全体周遊クルーズ）</t>
+  </si>
+  <si>
+    <t>発着地に戻る湾内クルーズ</t>
   </si>
 </sst>
 </file>
@@ -4616,7 +4663,7 @@
         <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>1286</v>
+        <v>1282</v>
       </c>
       <c r="E4">
         <v>8</v>
@@ -4630,7 +4677,7 @@
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>1286</v>
+        <v>1282</v>
       </c>
       <c r="C5" t="s">
         <v>7</v>
@@ -4690,7 +4737,7 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>1286</v>
+        <v>1282</v>
       </c>
       <c r="C8" t="s">
         <v>7</v>
@@ -4702,7 +4749,7 @@
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -4716,7 +4763,7 @@
         <v>12</v>
       </c>
       <c r="D9" t="s">
-        <v>1286</v>
+        <v>1282</v>
       </c>
       <c r="E9">
         <v>8</v>
@@ -4730,39 +4777,39 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>1286</v>
+        <v>1282</v>
       </c>
       <c r="C10" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="D10" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="E10">
         <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="B11" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="C11" t="s">
         <v>12</v>
       </c>
       <c r="D11" t="s">
-        <v>1286</v>
+        <v>1282</v>
       </c>
       <c r="E11">
         <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -4773,24 +4820,24 @@
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="D12" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="E12">
         <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="B13" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="C13" t="s">
         <v>7</v>
@@ -4802,7 +4849,7 @@
         <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -4813,24 +4860,24 @@
         <v>10</v>
       </c>
       <c r="C14" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="D14" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="E14">
         <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="B15" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="C15" t="s">
         <v>7</v>
@@ -4842,7 +4889,7 @@
         <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -4862,7 +4909,7 @@
         <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -4882,7 +4929,7 @@
         <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -4893,7 +4940,7 @@
         <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="D18" t="s">
         <v>36</v>
@@ -4907,7 +4954,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="B19" t="s">
         <v>36</v>
@@ -5056,7 +5103,7 @@
         <v>18</v>
       </c>
       <c r="D26" t="s">
-        <v>1283</v>
+        <v>1278</v>
       </c>
       <c r="E26">
         <v>10</v>
@@ -5070,13 +5117,13 @@
         <v>18</v>
       </c>
       <c r="B27" t="s">
-        <v>1283</v>
+        <v>1278</v>
       </c>
       <c r="C27" t="s">
         <v>34</v>
       </c>
       <c r="D27" t="s">
-        <v>43</v>
+        <v>1296</v>
       </c>
       <c r="E27">
         <v>12</v>
@@ -5097,6 +5144,9 @@
   <sheetFormatPr defaultRowHeight="13.3" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="29.4609375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="23.61328125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -5122,30 +5172,30 @@
         <v>64</v>
       </c>
       <c r="H1" t="s">
-        <v>1140</v>
+        <v>1304</v>
       </c>
       <c r="I1" t="s">
-        <v>1286</v>
+        <v>1303</v>
       </c>
       <c r="J1" t="s">
-        <v>1286</v>
+        <v>1305</v>
       </c>
       <c r="K1" t="s">
-        <v>1141</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="B2" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="C2" t="s">
         <v>147</v>
       </c>
       <c r="F2" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="H2" s="2">
         <v>0.375</v>
@@ -5162,16 +5212,16 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1145</v>
+        <v>1143</v>
       </c>
       <c r="B3" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="C3" t="s">
         <v>147</v>
       </c>
       <c r="F3" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="H3" s="2">
         <v>0.4236111111111111</v>
@@ -5188,16 +5238,16 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1147</v>
+        <v>1145</v>
       </c>
       <c r="B4" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="C4" t="s">
         <v>147</v>
       </c>
       <c r="F4" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="H4" s="2">
         <v>0.46527777777777779</v>
@@ -5214,16 +5264,16 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="B5" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="C5" t="s">
         <v>147</v>
       </c>
       <c r="F5" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="H5" s="2">
         <v>0.54861111111111116</v>
@@ -5240,16 +5290,16 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1151</v>
+        <v>1149</v>
       </c>
       <c r="B6" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="C6" t="s">
         <v>147</v>
       </c>
       <c r="F6" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="H6" s="2">
         <v>0.59027777777777779</v>
@@ -5266,16 +5316,16 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="B7" t="s">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="C7" t="s">
         <v>147</v>
       </c>
       <c r="F7" t="s">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="H7" s="2">
         <v>0.63194444444444442</v>
@@ -5292,16 +5342,16 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="B8" t="s">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="C8" t="s">
         <v>147</v>
       </c>
       <c r="F8" t="s">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="H8" s="2">
         <v>0.67361111111111116</v>
@@ -5355,18 +5405,18 @@
         <v>64</v>
       </c>
       <c r="H1" t="s">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="I1" t="s">
-        <v>1160</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="B2" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="C2" t="s">
         <v>147</v>
@@ -5380,10 +5430,10 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="B3" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="C3" t="s">
         <v>147</v>
@@ -5397,19 +5447,19 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C4" t="s">
         <v>1163</v>
       </c>
-      <c r="B4" t="s">
+      <c r="F4" t="s">
         <v>1164</v>
       </c>
-      <c r="C4" t="s">
+      <c r="G4" t="s">
         <v>1165</v>
-      </c>
-      <c r="F4" t="s">
-        <v>1166</v>
-      </c>
-      <c r="G4" t="s">
-        <v>1167</v>
       </c>
       <c r="H4" s="2">
         <v>0.5</v>
@@ -5420,10 +5470,10 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="B5" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="C5" t="s">
         <v>147</v>
@@ -5437,19 +5487,19 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="B6" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="C6" t="s">
+        <v>1163</v>
+      </c>
+      <c r="F6" t="s">
+        <v>1164</v>
+      </c>
+      <c r="G6" t="s">
         <v>1165</v>
-      </c>
-      <c r="F6" t="s">
-        <v>1166</v>
-      </c>
-      <c r="G6" t="s">
-        <v>1167</v>
       </c>
       <c r="H6" s="2">
         <v>0.60416666666666663</v>
@@ -5460,10 +5510,10 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1171</v>
+        <v>1169</v>
       </c>
       <c r="B7" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="C7" t="s">
         <v>147</v>
@@ -5509,21 +5559,21 @@
         <v>64</v>
       </c>
       <c r="H1" t="s">
+        <v>1170</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1171</v>
+      </c>
+      <c r="J1" t="s">
         <v>1172</v>
-      </c>
-      <c r="I1" t="s">
-        <v>1173</v>
-      </c>
-      <c r="J1" t="s">
-        <v>1174</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1175</v>
+        <v>1173</v>
       </c>
       <c r="B2" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="C2" t="s">
         <v>147</v>
@@ -5540,10 +5590,10 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1177</v>
+        <v>1175</v>
       </c>
       <c r="B3" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="C3" t="s">
         <v>147</v>
@@ -5560,10 +5610,10 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1179</v>
+        <v>1177</v>
       </c>
       <c r="B4" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="C4" t="s">
         <v>147</v>
@@ -5580,10 +5630,10 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1181</v>
+        <v>1179</v>
       </c>
       <c r="B5" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="C5" t="s">
         <v>147</v>
@@ -5600,10 +5650,10 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="B6" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="C6" t="s">
         <v>147</v>
@@ -5620,10 +5670,10 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1185</v>
+        <v>1183</v>
       </c>
       <c r="B7" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="C7" t="s">
         <v>147</v>
@@ -5672,21 +5722,21 @@
         <v>64</v>
       </c>
       <c r="H1" t="s">
-        <v>1187</v>
+        <v>1185</v>
       </c>
       <c r="I1" t="s">
-        <v>1173</v>
+        <v>1171</v>
       </c>
       <c r="J1" t="s">
-        <v>1188</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1189</v>
+        <v>1187</v>
       </c>
       <c r="B2" t="s">
-        <v>1176</v>
+        <v>1174</v>
       </c>
       <c r="C2" t="s">
         <v>147</v>
@@ -5703,10 +5753,10 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1190</v>
+        <v>1188</v>
       </c>
       <c r="B3" t="s">
-        <v>1178</v>
+        <v>1176</v>
       </c>
       <c r="C3" t="s">
         <v>147</v>
@@ -5723,10 +5773,10 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="B4" t="s">
-        <v>1180</v>
+        <v>1178</v>
       </c>
       <c r="C4" t="s">
         <v>147</v>
@@ -5743,10 +5793,10 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="B5" t="s">
-        <v>1182</v>
+        <v>1180</v>
       </c>
       <c r="C5" t="s">
         <v>147</v>
@@ -5763,10 +5813,10 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1193</v>
+        <v>1191</v>
       </c>
       <c r="B6" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="C6" t="s">
         <v>147</v>
@@ -5783,10 +5833,10 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1194</v>
+        <v>1192</v>
       </c>
       <c r="B7" t="s">
-        <v>1186</v>
+        <v>1184</v>
       </c>
       <c r="C7" t="s">
         <v>147</v>
@@ -5838,43 +5888,43 @@
         <v>53</v>
       </c>
       <c r="I1" t="s">
+        <v>1193</v>
+      </c>
+      <c r="J1" t="s">
+        <v>1194</v>
+      </c>
+      <c r="K1" t="s">
         <v>1195</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>1196</v>
       </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
         <v>1197</v>
       </c>
-      <c r="L1" t="s">
+      <c r="N1" t="s">
         <v>1198</v>
       </c>
-      <c r="M1" t="s">
+      <c r="O1" t="s">
         <v>1199</v>
       </c>
-      <c r="N1" t="s">
+      <c r="P1" t="s">
         <v>1200</v>
       </c>
-      <c r="O1" t="s">
+      <c r="Q1" t="s">
         <v>1201</v>
       </c>
-      <c r="P1" t="s">
+      <c r="R1" t="s">
         <v>1202</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="S1" t="s">
         <v>1203</v>
       </c>
-      <c r="R1" t="s">
+      <c r="T1" t="s">
         <v>1204</v>
       </c>
-      <c r="S1" t="s">
+      <c r="U1" t="s">
         <v>1205</v>
-      </c>
-      <c r="T1" t="s">
-        <v>1206</v>
-      </c>
-      <c r="U1" t="s">
-        <v>1207</v>
       </c>
       <c r="V1" t="s">
         <v>50</v>
@@ -5882,10 +5932,10 @@
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="B2" t="s">
-        <v>1209</v>
+        <v>1207</v>
       </c>
       <c r="C2" t="s">
         <v>147</v>
@@ -5899,10 +5949,10 @@
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1210</v>
+        <v>1208</v>
       </c>
       <c r="B3" t="s">
-        <v>1211</v>
+        <v>1209</v>
       </c>
       <c r="C3" t="s">
         <v>147</v>
@@ -5934,10 +5984,10 @@
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1212</v>
+        <v>1210</v>
       </c>
       <c r="B4" t="s">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="C4" t="s">
         <v>147</v>
@@ -5987,10 +6037,10 @@
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1214</v>
+        <v>1212</v>
       </c>
       <c r="B5" t="s">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="C5" t="s">
         <v>147</v>
@@ -6040,10 +6090,10 @@
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="B6" t="s">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="C6" t="s">
         <v>147</v>
@@ -6119,43 +6169,43 @@
         <v>50</v>
       </c>
       <c r="I1" t="s">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="J1" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="K1" t="s">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="L1" t="s">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="M1" t="s">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="N1" t="s">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="O1" t="s">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="P1" t="s">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="Q1" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="R1" t="s">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="S1" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="T1" t="s">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="U1" t="s">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="V1" t="s">
         <v>53</v>
@@ -6163,10 +6213,10 @@
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="B2" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
       <c r="C2" t="s">
         <v>147</v>
@@ -6207,10 +6257,10 @@
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="B3" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="C3" t="s">
         <v>147</v>
@@ -6254,10 +6304,10 @@
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="B4" t="s">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="C4" t="s">
         <v>147</v>
@@ -6307,10 +6357,10 @@
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="B5" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="C5" t="s">
         <v>147</v>
@@ -6360,10 +6410,10 @@
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="B6" t="s">
-        <v>1152</v>
+        <v>1150</v>
       </c>
       <c r="C6" t="s">
         <v>147</v>
@@ -6415,94 +6465,94 @@
   <sheetData>
     <row r="1" spans="1:42" x14ac:dyDescent="0.25">
       <c r="B1" s="3" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>1223</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>1224</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>1225</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>1226</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>1227</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>1228</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>1229</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>1230</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>1231</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>1232</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>1233</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>1234</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>1235</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>1236</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>1237</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>1238</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>1239</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>1240</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>1241</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>1242</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>1243</v>
-      </c>
-      <c r="W1" s="3" t="s">
-        <v>1244</v>
-      </c>
-      <c r="X1" s="3" t="s">
-        <v>1245</v>
       </c>
       <c r="Y1" s="3" t="s">
         <v>39</v>
       </c>
       <c r="Z1" s="3" t="s">
+        <v>1244</v>
+      </c>
+      <c r="AA1" s="3" t="s">
+        <v>1245</v>
+      </c>
+      <c r="AB1" s="3" t="s">
         <v>1246</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AC1" s="3" t="s">
         <v>1247</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AD1" s="3" t="s">
         <v>1248</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AE1" s="3" t="s">
         <v>1249</v>
-      </c>
-      <c r="AD1" s="3" t="s">
-        <v>1250</v>
-      </c>
-      <c r="AE1" s="3" t="s">
-        <v>1251</v>
       </c>
       <c r="AF1" s="3" t="s">
         <v>35</v>
@@ -6517,30 +6567,30 @@
         <v>52</v>
       </c>
       <c r="AJ1" s="3" t="s">
+        <v>1250</v>
+      </c>
+      <c r="AK1" s="3" t="s">
+        <v>1251</v>
+      </c>
+      <c r="AL1" s="3" t="s">
         <v>1252</v>
       </c>
-      <c r="AK1" s="3" t="s">
+      <c r="AM1" s="3" t="s">
         <v>1253</v>
       </c>
-      <c r="AL1" s="3" t="s">
+      <c r="AN1" s="3" t="s">
         <v>1254</v>
       </c>
-      <c r="AM1" s="3" t="s">
+      <c r="AO1" s="3" t="s">
         <v>1255</v>
       </c>
-      <c r="AN1" s="3" t="s">
+      <c r="AP1" s="3" t="s">
         <v>1256</v>
-      </c>
-      <c r="AO1" s="3" t="s">
-        <v>1257</v>
-      </c>
-      <c r="AP1" s="3" t="s">
-        <v>1258</v>
       </c>
     </row>
     <row r="2" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -6668,7 +6718,7 @@
     </row>
     <row r="3" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="B3">
         <v>290</v>
@@ -6796,7 +6846,7 @@
     </row>
     <row r="4" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="B4">
         <v>440</v>
@@ -6924,7 +6974,7 @@
     </row>
     <row r="5" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="B5">
         <v>440</v>
@@ -7052,7 +7102,7 @@
     </row>
     <row r="6" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="B6">
         <v>510</v>
@@ -7180,7 +7230,7 @@
     </row>
     <row r="7" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="B7">
         <v>610</v>
@@ -7308,7 +7358,7 @@
     </row>
     <row r="8" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="B8">
         <v>790</v>
@@ -7436,7 +7486,7 @@
     </row>
     <row r="9" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="B9">
         <v>940</v>
@@ -7564,7 +7614,7 @@
     </row>
     <row r="10" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="B10">
         <v>1120</v>
@@ -7692,7 +7742,7 @@
     </row>
     <row r="11" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="B11">
         <v>1210</v>
@@ -7820,7 +7870,7 @@
     </row>
     <row r="12" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="B12">
         <v>1370</v>
@@ -7948,7 +7998,7 @@
     </row>
     <row r="13" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="B13">
         <v>1370</v>
@@ -8076,7 +8126,7 @@
     </row>
     <row r="14" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>1235</v>
+        <v>1233</v>
       </c>
       <c r="B14">
         <v>1510</v>
@@ -8204,7 +8254,7 @@
     </row>
     <row r="15" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>1236</v>
+        <v>1234</v>
       </c>
       <c r="B15">
         <v>1600</v>
@@ -8332,7 +8382,7 @@
     </row>
     <row r="16" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="B16">
         <v>1700</v>
@@ -8460,7 +8510,7 @@
     </row>
     <row r="17" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>1238</v>
+        <v>1236</v>
       </c>
       <c r="B17">
         <v>1860</v>
@@ -8588,7 +8638,7 @@
     </row>
     <row r="18" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>1239</v>
+        <v>1237</v>
       </c>
       <c r="B18">
         <v>1940</v>
@@ -8716,7 +8766,7 @@
     </row>
     <row r="19" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>1240</v>
+        <v>1238</v>
       </c>
       <c r="B19">
         <v>1940</v>
@@ -8844,7 +8894,7 @@
     </row>
     <row r="20" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>1241</v>
+        <v>1239</v>
       </c>
       <c r="B20">
         <v>2220</v>
@@ -8972,7 +9022,7 @@
     </row>
     <row r="21" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>1242</v>
+        <v>1240</v>
       </c>
       <c r="B21">
         <v>2280</v>
@@ -9100,7 +9150,7 @@
     </row>
     <row r="22" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>1243</v>
+        <v>1241</v>
       </c>
       <c r="B22">
         <v>2350</v>
@@ -9228,7 +9278,7 @@
     </row>
     <row r="23" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="B23">
         <v>2480</v>
@@ -9356,7 +9406,7 @@
     </row>
     <row r="24" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="B24">
         <v>2480</v>
@@ -9612,7 +9662,7 @@
     </row>
     <row r="26" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="B26">
         <v>2610</v>
@@ -9740,7 +9790,7 @@
     </row>
     <row r="27" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="B27">
         <v>2680</v>
@@ -9868,7 +9918,7 @@
     </row>
     <row r="28" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="B28">
         <v>2750</v>
@@ -9996,7 +10046,7 @@
     </row>
     <row r="29" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>1249</v>
+        <v>1247</v>
       </c>
       <c r="B29">
         <v>2820</v>
@@ -10124,7 +10174,7 @@
     </row>
     <row r="30" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
       <c r="B30">
         <v>2890</v>
@@ -10252,7 +10302,7 @@
     </row>
     <row r="31" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="B31">
         <v>3020</v>
@@ -10892,7 +10942,7 @@
     </row>
     <row r="36" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="B36">
         <v>3620</v>
@@ -11020,7 +11070,7 @@
     </row>
     <row r="37" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="B37">
         <v>3690</v>
@@ -11148,7 +11198,7 @@
     </row>
     <row r="38" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="B38">
         <v>3820</v>
@@ -11276,7 +11326,7 @@
     </row>
     <row r="39" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="B39">
         <v>3820</v>
@@ -11404,7 +11454,7 @@
     </row>
     <row r="40" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="B40">
         <v>3890</v>
@@ -11532,7 +11582,7 @@
     </row>
     <row r="41" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="B41">
         <v>3960</v>
@@ -11660,7 +11710,7 @@
     </row>
     <row r="42" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="B42">
         <v>4160</v>
@@ -12010,16 +12060,16 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>1257</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1258</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1261</v>
+      </c>
+      <c r="D12" t="s">
         <v>1259</v>
-      </c>
-      <c r="B12" t="s">
-        <v>1260</v>
-      </c>
-      <c r="C12" t="s">
-        <v>1263</v>
-      </c>
-      <c r="D12" t="s">
-        <v>1261</v>
       </c>
       <c r="E12">
         <v>620</v>
@@ -12118,249 +12168,358 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9E270AA-17A2-4D2C-AEFB-5A166D0C1BBB}">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="13.3" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.3828125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="30.07421875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="30.07421875" customWidth="1"/>
-    <col min="6" max="6" width="14.53515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.921875" customWidth="1"/>
+    <col min="4" max="4" width="11.4609375" customWidth="1"/>
+    <col min="5" max="6" width="30.07421875" customWidth="1"/>
+    <col min="8" max="8" width="14.53515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1264</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1297</v>
+      </c>
+      <c r="D1" t="s">
         <v>1298</v>
       </c>
-      <c r="B1" t="s">
+      <c r="E1" t="s">
+        <v>1283</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1276</v>
+      </c>
+      <c r="G1" t="s">
+        <v>1265</v>
+      </c>
+      <c r="H1" t="s">
         <v>1266</v>
       </c>
-      <c r="C1" t="s">
+      <c r="I1" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1284</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1299</v>
+      </c>
+      <c r="D2">
+        <v>30</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1280</v>
+      </c>
+      <c r="F2" t="s">
+        <v>1284</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1308</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1300</v>
+      </c>
+      <c r="D3">
+        <v>40</v>
+      </c>
+      <c r="E3" t="s">
+        <v>1306</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3">
+        <v>1500</v>
+      </c>
+      <c r="H3">
+        <v>1350</v>
+      </c>
+      <c r="I3" t="s">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1307</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1300</v>
+      </c>
+      <c r="D4">
+        <v>10</v>
+      </c>
+      <c r="E4" t="s">
+        <v>1306</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4">
+        <v>1500</v>
+      </c>
+      <c r="H4">
+        <v>1350</v>
+      </c>
+      <c r="I4" t="s">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1311</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1300</v>
+      </c>
+      <c r="D5">
+        <v>60</v>
+      </c>
+      <c r="E5" t="s">
+        <v>1306</v>
+      </c>
+      <c r="F5" t="s">
+        <v>1281</v>
+      </c>
+      <c r="G5">
+        <v>1500</v>
+      </c>
+      <c r="H5">
+        <v>1350</v>
+      </c>
+      <c r="I5" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1267</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1299</v>
+      </c>
+      <c r="D6" s="2">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="E6" t="s">
+        <v>1267</v>
+      </c>
+      <c r="F6" t="s">
+        <v>1272</v>
+      </c>
+      <c r="G6">
+        <v>2000</v>
+      </c>
+      <c r="H6">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1285</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1299</v>
+      </c>
+      <c r="D7" s="2">
+        <v>6.25E-2</v>
+      </c>
+      <c r="E7" t="s">
+        <v>1291</v>
+      </c>
+      <c r="F7" t="s">
+        <v>1290</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1299</v>
+      </c>
+      <c r="D8" s="2">
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1279</v>
+      </c>
+      <c r="F8" t="s">
+        <v>1277</v>
+      </c>
+      <c r="G8">
+        <v>1100</v>
+      </c>
+      <c r="H8">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1301</v>
+      </c>
+      <c r="D9" s="2">
+        <v>3.4722222222222224E-2</v>
+      </c>
+      <c r="E9" t="s">
+        <v>1268</v>
+      </c>
+      <c r="F9" t="s">
+        <v>1278</v>
+      </c>
+      <c r="G9">
+        <v>2500</v>
+      </c>
+      <c r="H9">
+        <v>2250</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1301</v>
+      </c>
+      <c r="D10" s="2">
+        <v>5.5555555555555552E-2</v>
+      </c>
+      <c r="E10" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10" t="s">
+        <v>1171</v>
+      </c>
+      <c r="G10">
+        <v>3800</v>
+      </c>
+      <c r="H10">
+        <v>3800</v>
+      </c>
+      <c r="I10" t="s">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1286</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1299</v>
+      </c>
+      <c r="D11">
+        <v>30</v>
+      </c>
+      <c r="E11" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" t="s">
+        <v>1287</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1269</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1299</v>
+      </c>
+      <c r="D12">
+        <v>30</v>
+      </c>
+      <c r="E12" t="s">
         <v>1288</v>
       </c>
-      <c r="D1" t="s">
-        <v>1278</v>
-      </c>
-      <c r="E1" t="s">
-        <v>1267</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1268</v>
-      </c>
-      <c r="G1" t="s">
-        <v>1272</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>1295</v>
-      </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B13" t="s">
         <v>1289</v>
       </c>
-      <c r="C2" t="s">
-        <v>1285</v>
-      </c>
-      <c r="D2" t="s">
-        <v>1289</v>
-      </c>
-      <c r="E2">
+      <c r="C13" t="s">
+        <v>1299</v>
+      </c>
+      <c r="D13" s="2">
+        <v>6.25E-2</v>
+      </c>
+      <c r="E13" t="s">
+        <v>1291</v>
+      </c>
+      <c r="F13" t="s">
+        <v>1292</v>
+      </c>
+      <c r="G13">
         <v>0</v>
       </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>1295</v>
-      </c>
-      <c r="B3" t="s">
-        <v>1281</v>
-      </c>
-      <c r="C3" t="s">
-        <v>1285</v>
-      </c>
-      <c r="D3" t="s">
-        <v>1280</v>
-      </c>
-      <c r="E3">
-        <v>1500</v>
-      </c>
-      <c r="F3">
-        <v>1350</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>1295</v>
-      </c>
-      <c r="B4" t="s">
-        <v>1282</v>
-      </c>
-      <c r="C4" t="s">
-        <v>1287</v>
-      </c>
-      <c r="D4" t="s">
-        <v>1286</v>
-      </c>
-      <c r="E4">
-        <v>1500</v>
-      </c>
-      <c r="F4">
-        <v>1350</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>1295</v>
-      </c>
-      <c r="B5" t="s">
-        <v>1269</v>
-      </c>
-      <c r="C5" t="s">
-        <v>1269</v>
-      </c>
-      <c r="D5" t="s">
-        <v>1274</v>
-      </c>
-      <c r="E5">
-        <v>2000</v>
-      </c>
-      <c r="F5">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>1295</v>
-      </c>
-      <c r="B6" t="s">
-        <v>1290</v>
-      </c>
-      <c r="C6" t="s">
-        <v>1296</v>
-      </c>
-      <c r="D6" t="s">
-        <v>1295</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>1299</v>
-      </c>
-      <c r="B7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C7" t="s">
-        <v>1284</v>
-      </c>
-      <c r="D7" t="s">
-        <v>1279</v>
-      </c>
-      <c r="E7">
-        <v>1100</v>
-      </c>
-      <c r="F7">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>1300</v>
-      </c>
-      <c r="B8" t="s">
-        <v>1270</v>
-      </c>
-      <c r="C8" t="s">
-        <v>1270</v>
-      </c>
-      <c r="D8" t="s">
-        <v>1283</v>
-      </c>
-      <c r="E8">
-        <v>2500</v>
-      </c>
-      <c r="F8">
-        <v>2250</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>1300</v>
-      </c>
-      <c r="B9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" t="s">
-        <v>1173</v>
-      </c>
-      <c r="E9">
-        <v>3800</v>
-      </c>
-      <c r="F9">
-        <v>3800</v>
-      </c>
-      <c r="G9" t="s">
-        <v>1273</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>1300</v>
-      </c>
-      <c r="B10" t="s">
-        <v>1291</v>
-      </c>
-      <c r="C10" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" t="s">
-        <v>1292</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>1297</v>
-      </c>
-      <c r="B11" t="s">
-        <v>1271</v>
-      </c>
-      <c r="C11" t="s">
-        <v>1293</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>1297</v>
-      </c>
-      <c r="B12" t="s">
-        <v>1294</v>
-      </c>
-      <c r="C12" t="s">
-        <v>1296</v>
-      </c>
-      <c r="D12" t="s">
-        <v>1297</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
+      <c r="H13">
         <v>0</v>
       </c>
     </row>

--- a/統合版・2026年三陸鉄道周辺ダイヤ_4_2.xlsx
+++ b/統合版・2026年三陸鉄道周辺ダイヤ_4_2.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dnaka_cy7a7ax\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{466DCCEB-D8D1-4C37-9192-E74F99F16200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34088BE4-B67A-4D62-A884-119B53C79025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="16371" yWindow="0" windowWidth="14915" windowHeight="11709" activeTab="2" xr2:uid="{3339B9FF-A08C-4853-B3B5-D870D1D967CF}"/>
-    <workbookView xWindow="16354" yWindow="-103" windowWidth="29692" windowHeight="11829" activeTab="2" xr2:uid="{EECD383A-838A-41CD-8AB1-343EAFF88011}"/>
+    <workbookView minimized="1" xWindow="30223" yWindow="1851" windowWidth="4697" windowHeight="9103" activeTab="2" xr2:uid="{EECD383A-838A-41CD-8AB1-343EAFF88011}"/>
   </bookViews>
   <sheets>
     <sheet name="乗換設定" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3086" uniqueCount="1383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3081" uniqueCount="1383">
   <si>
     <t>事業者</t>
   </si>
@@ -4364,10 +4364,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>琥珀博物館</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>久慈琥珀博物館入口</t>
     <rPh sb="7" eb="9">
       <t>イリグチ</t>
@@ -4443,6 +4439,13 @@
     </rPh>
     <rPh sb="7" eb="8">
       <t>マエ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>久慈琥珀博物館</t>
+    <rPh sb="0" eb="2">
+      <t>クジ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -4939,7 +4942,7 @@
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -4959,7 +4962,7 @@
         <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -4979,7 +4982,7 @@
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -4999,7 +5002,7 @@
         <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -5019,7 +5022,7 @@
         <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -5039,7 +5042,7 @@
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -5059,7 +5062,7 @@
         <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>1377</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -5119,7 +5122,7 @@
         <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>1378</v>
+        <v>1377</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -5199,7 +5202,7 @@
         <v>12</v>
       </c>
       <c r="F17" t="s">
-        <v>1379</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -5290,16 +5293,16 @@
         <v>1366</v>
       </c>
       <c r="C22" t="s">
+        <v>1380</v>
+      </c>
+      <c r="D22" t="s">
         <v>1381</v>
-      </c>
-      <c r="D22" t="s">
-        <v>1382</v>
       </c>
       <c r="E22">
         <v>20</v>
       </c>
       <c r="F22" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -5307,19 +5310,19 @@
         <v>1367</v>
       </c>
       <c r="B23" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="C23" t="s">
+        <v>1380</v>
+      </c>
+      <c r="D23" t="s">
         <v>1381</v>
-      </c>
-      <c r="D23" t="s">
-        <v>1382</v>
       </c>
       <c r="E23">
         <v>20</v>
       </c>
       <c r="F23" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
     </row>
   </sheetData>
@@ -13129,11 +13132,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9E270AA-17A2-4D2C-AEFB-5A166D0C1BBB}">
-  <dimension ref="A1:K14"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultRowHeight="13.3" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.3828125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.07421875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.61328125" customWidth="1"/>
     <col min="3" max="3" width="13.921875" customWidth="1"/>
     <col min="4" max="4" width="11.4609375" customWidth="1"/>
     <col min="5" max="6" width="30.07421875" customWidth="1"/>
@@ -13453,7 +13456,7 @@
         <v>1277</v>
       </c>
       <c r="B12" t="s">
-        <v>1372</v>
+        <v>1382</v>
       </c>
       <c r="C12" t="s">
         <v>1283</v>
@@ -13462,10 +13465,10 @@
         <v>60</v>
       </c>
       <c r="E12" t="s">
-        <v>1273</v>
+        <v>1380</v>
       </c>
       <c r="F12" t="s">
-        <v>1366</v>
+        <v>1381</v>
       </c>
       <c r="G12">
         <v>500</v>
@@ -13485,56 +13488,24 @@
         <v>1277</v>
       </c>
       <c r="B13" t="s">
-        <v>1372</v>
+        <v>1274</v>
       </c>
       <c r="C13" t="s">
         <v>1283</v>
       </c>
-      <c r="D13">
-        <v>60</v>
+      <c r="D13" s="2">
+        <v>6.25E-2</v>
       </c>
       <c r="E13" t="s">
-        <v>1381</v>
+        <v>1276</v>
       </c>
       <c r="F13" t="s">
-        <v>1382</v>
+        <v>1277</v>
       </c>
       <c r="G13">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="H13">
-        <v>400</v>
-      </c>
-      <c r="I13">
-        <v>200</v>
-      </c>
-      <c r="J13">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>1277</v>
-      </c>
-      <c r="B14" t="s">
-        <v>1274</v>
-      </c>
-      <c r="C14" t="s">
-        <v>1283</v>
-      </c>
-      <c r="D14" s="2">
-        <v>6.25E-2</v>
-      </c>
-      <c r="E14" t="s">
-        <v>1276</v>
-      </c>
-      <c r="F14" t="s">
-        <v>1277</v>
-      </c>
-      <c r="G14">
-        <v>0</v>
-      </c>
-      <c r="H14">
         <v>0</v>
       </c>
     </row>

--- a/統合版・2026年三陸鉄道周辺ダイヤ_4_2.xlsx
+++ b/統合版・2026年三陸鉄道周辺ダイヤ_4_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dnaka_cy7a7ax\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34088BE4-B67A-4D62-A884-119B53C79025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{662EE79B-5FA0-482B-821D-061A79A77B95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="16371" yWindow="0" windowWidth="14915" windowHeight="11709" activeTab="2" xr2:uid="{3339B9FF-A08C-4853-B3B5-D870D1D967CF}"/>
     <workbookView minimized="1" xWindow="30223" yWindow="1851" windowWidth="4697" windowHeight="9103" activeTab="2" xr2:uid="{EECD383A-838A-41CD-8AB1-343EAFF88011}"/>
@@ -4097,19 +4097,10 @@
     <t>宮古うみねこ丸便</t>
   </si>
   <si>
-    <t>宮古うみねこ丸（片道移動）</t>
-  </si>
-  <si>
-    <t>宮古うみねこ丸（湾内周遊＋移動）</t>
-  </si>
-  <si>
     <t>出崎ふ頭発⇒湾内周遊⇒浄土ヶ浜下船</t>
   </si>
   <si>
     <t>出崎ふ頭・浄土ヶ浜間のショートカット</t>
-  </si>
-  <si>
-    <t>宮古うみねこ丸（全体周遊クルーズ）</t>
   </si>
   <si>
     <t>発着地に戻る湾内クルーズ</t>
@@ -4446,6 +4437,27 @@
     <t>久慈琥珀博物館</t>
     <rPh sb="0" eb="2">
       <t>クジ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>宮古うみねこ丸（湾内周遊＋移動（出崎ふ頭→浄土ヶ浜））</t>
+    <rPh sb="16" eb="18">
+      <t>デサキ</t>
+    </rPh>
+    <rPh sb="21" eb="25">
+      <t>ジョウドガハマ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>宮古うみねこ丸（片道移動（出崎ふ頭→浄土ヶ浜））</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>宮古うみねこ丸（全体周遊クルーズ（出崎ふ頭発））</t>
+    <rPh sb="21" eb="22">
+      <t>ハツ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -4942,7 +4954,7 @@
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>1373</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -4962,7 +4974,7 @@
         <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>1373</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -4982,7 +4994,7 @@
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>1373</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -5002,7 +5014,7 @@
         <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>1374</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -5022,7 +5034,7 @@
         <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>1375</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -5042,7 +5054,7 @@
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>1375</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -5062,7 +5074,7 @@
         <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>1376</v>
+        <v>1373</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -5122,7 +5134,7 @@
         <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>1377</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -5202,7 +5214,7 @@
         <v>12</v>
       </c>
       <c r="F17" t="s">
-        <v>1378</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -5216,7 +5228,7 @@
         <v>1273</v>
       </c>
       <c r="D18" t="s">
-        <v>1370</v>
+        <v>1367</v>
       </c>
       <c r="E18">
         <v>5</v>
@@ -5230,13 +5242,13 @@
         <v>1273</v>
       </c>
       <c r="B19" t="s">
-        <v>1370</v>
+        <v>1367</v>
       </c>
       <c r="C19" t="s">
         <v>34</v>
       </c>
       <c r="D19" t="s">
-        <v>1371</v>
+        <v>1368</v>
       </c>
       <c r="E19">
         <v>10</v>
@@ -5253,10 +5265,10 @@
         <v>1277</v>
       </c>
       <c r="C20" t="s">
+        <v>1364</v>
+      </c>
+      <c r="D20" t="s">
         <v>1367</v>
-      </c>
-      <c r="D20" t="s">
-        <v>1370</v>
       </c>
       <c r="E20">
         <v>5</v>
@@ -5267,16 +5279,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B21" t="s">
         <v>1367</v>
-      </c>
-      <c r="B21" t="s">
-        <v>1370</v>
       </c>
       <c r="C21" t="s">
         <v>34</v>
       </c>
       <c r="D21" t="s">
-        <v>1371</v>
+        <v>1368</v>
       </c>
       <c r="E21">
         <v>10</v>
@@ -5290,39 +5302,39 @@
         <v>1273</v>
       </c>
       <c r="B22" t="s">
-        <v>1366</v>
+        <v>1363</v>
       </c>
       <c r="C22" t="s">
-        <v>1380</v>
+        <v>1377</v>
       </c>
       <c r="D22" t="s">
-        <v>1381</v>
+        <v>1378</v>
       </c>
       <c r="E22">
         <v>20</v>
       </c>
       <c r="F22" t="s">
-        <v>1379</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1367</v>
+        <v>1364</v>
       </c>
       <c r="B23" t="s">
-        <v>1372</v>
+        <v>1369</v>
       </c>
       <c r="C23" t="s">
-        <v>1380</v>
+        <v>1377</v>
       </c>
       <c r="D23" t="s">
-        <v>1381</v>
+        <v>1378</v>
       </c>
       <c r="E23">
         <v>20</v>
       </c>
       <c r="F23" t="s">
-        <v>1379</v>
+        <v>1376</v>
       </c>
     </row>
   </sheetData>
@@ -6679,18 +6691,18 @@
         <v>55</v>
       </c>
       <c r="H1" t="s">
-        <v>1297</v>
+        <v>1294</v>
       </c>
       <c r="I1" t="s">
-        <v>1298</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1299</v>
+        <v>1296</v>
       </c>
       <c r="B2" t="s">
-        <v>1300</v>
+        <v>1297</v>
       </c>
       <c r="C2" t="s">
         <v>138</v>
@@ -6704,10 +6716,10 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1301</v>
+        <v>1298</v>
       </c>
       <c r="B3" t="s">
-        <v>1302</v>
+        <v>1299</v>
       </c>
       <c r="C3" t="s">
         <v>138</v>
@@ -6721,10 +6733,10 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1303</v>
+        <v>1300</v>
       </c>
       <c r="B4" t="s">
-        <v>1304</v>
+        <v>1301</v>
       </c>
       <c r="C4" t="s">
         <v>138</v>
@@ -6738,10 +6750,10 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1305</v>
+        <v>1302</v>
       </c>
       <c r="B5" t="s">
-        <v>1306</v>
+        <v>1303</v>
       </c>
       <c r="C5" t="s">
         <v>138</v>
@@ -6755,10 +6767,10 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1307</v>
+        <v>1304</v>
       </c>
       <c r="B6" t="s">
-        <v>1308</v>
+        <v>1305</v>
       </c>
       <c r="C6" t="s">
         <v>138</v>
@@ -6772,10 +6784,10 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1309</v>
+        <v>1306</v>
       </c>
       <c r="B7" t="s">
-        <v>1310</v>
+        <v>1307</v>
       </c>
       <c r="C7" t="s">
         <v>138</v>
@@ -6789,10 +6801,10 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1311</v>
+        <v>1308</v>
       </c>
       <c r="B8" t="s">
-        <v>1312</v>
+        <v>1309</v>
       </c>
       <c r="C8" t="s">
         <v>138</v>
@@ -6806,10 +6818,10 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1313</v>
+        <v>1310</v>
       </c>
       <c r="B9" t="s">
-        <v>1314</v>
+        <v>1311</v>
       </c>
       <c r="C9" t="s">
         <v>138</v>
@@ -6823,10 +6835,10 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1315</v>
+        <v>1312</v>
       </c>
       <c r="B10" t="s">
-        <v>1316</v>
+        <v>1313</v>
       </c>
       <c r="C10" t="s">
         <v>138</v>
@@ -6872,18 +6884,18 @@
         <v>55</v>
       </c>
       <c r="H1" t="s">
-        <v>1317</v>
+        <v>1314</v>
       </c>
       <c r="I1" t="s">
-        <v>1318</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1319</v>
+        <v>1316</v>
       </c>
       <c r="B2" t="s">
-        <v>1320</v>
+        <v>1317</v>
       </c>
       <c r="C2" t="s">
         <v>138</v>
@@ -6897,10 +6909,10 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1321</v>
+        <v>1318</v>
       </c>
       <c r="B3" t="s">
-        <v>1322</v>
+        <v>1319</v>
       </c>
       <c r="C3" t="s">
         <v>138</v>
@@ -6914,10 +6926,10 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1323</v>
+        <v>1320</v>
       </c>
       <c r="B4" t="s">
-        <v>1324</v>
+        <v>1321</v>
       </c>
       <c r="C4" t="s">
         <v>138</v>
@@ -6931,10 +6943,10 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1325</v>
+        <v>1322</v>
       </c>
       <c r="B5" t="s">
-        <v>1326</v>
+        <v>1323</v>
       </c>
       <c r="C5" t="s">
         <v>138</v>
@@ -6948,10 +6960,10 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1327</v>
+        <v>1324</v>
       </c>
       <c r="B6" t="s">
-        <v>1328</v>
+        <v>1325</v>
       </c>
       <c r="C6" t="s">
         <v>138</v>
@@ -6965,10 +6977,10 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1329</v>
+        <v>1326</v>
       </c>
       <c r="B7" t="s">
-        <v>1330</v>
+        <v>1327</v>
       </c>
       <c r="C7" t="s">
         <v>138</v>
@@ -7020,18 +7032,18 @@
         <v>55</v>
       </c>
       <c r="H1" t="s">
-        <v>1297</v>
+        <v>1294</v>
       </c>
       <c r="I1" t="s">
-        <v>1331</v>
+        <v>1328</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1332</v>
+        <v>1329</v>
       </c>
       <c r="B2" t="s">
-        <v>1333</v>
+        <v>1330</v>
       </c>
       <c r="C2" t="s">
         <v>1077</v>
@@ -7045,10 +7057,10 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1335</v>
+        <v>1332</v>
       </c>
       <c r="B3" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="C3" t="s">
         <v>1077</v>
@@ -7062,19 +7074,19 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1337</v>
+        <v>1334</v>
       </c>
       <c r="B4" t="s">
-        <v>1338</v>
+        <v>1335</v>
       </c>
       <c r="C4" t="s">
         <v>1097</v>
       </c>
       <c r="F4" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="G4" t="s">
-        <v>1340</v>
+        <v>1337</v>
       </c>
       <c r="H4" s="4">
         <v>0.39583333333333331</v>
@@ -7085,10 +7097,10 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1341</v>
+        <v>1338</v>
       </c>
       <c r="B5" t="s">
-        <v>1342</v>
+        <v>1339</v>
       </c>
       <c r="C5" t="s">
         <v>138</v>
@@ -7102,10 +7114,10 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1343</v>
+        <v>1340</v>
       </c>
       <c r="B6" t="s">
-        <v>1344</v>
+        <v>1341</v>
       </c>
       <c r="C6" t="s">
         <v>1077</v>
@@ -7119,10 +7131,10 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1345</v>
+        <v>1342</v>
       </c>
       <c r="B7" t="s">
-        <v>1346</v>
+        <v>1343</v>
       </c>
       <c r="C7" t="s">
         <v>1077</v>
@@ -7136,19 +7148,19 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1347</v>
+        <v>1344</v>
       </c>
       <c r="B8" t="s">
-        <v>1348</v>
+        <v>1345</v>
       </c>
       <c r="C8" t="s">
         <v>1097</v>
       </c>
       <c r="F8" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="G8" t="s">
-        <v>1340</v>
+        <v>1337</v>
       </c>
       <c r="H8" s="4">
         <v>0.57847222222222228</v>
@@ -7159,10 +7171,10 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1349</v>
+        <v>1346</v>
       </c>
       <c r="B9" t="s">
-        <v>1350</v>
+        <v>1347</v>
       </c>
       <c r="C9" t="s">
         <v>138</v>
@@ -7176,10 +7188,10 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1351</v>
+        <v>1348</v>
       </c>
       <c r="B10" t="s">
-        <v>1352</v>
+        <v>1349</v>
       </c>
       <c r="C10" t="s">
         <v>1077</v>
@@ -7225,21 +7237,21 @@
         <v>55</v>
       </c>
       <c r="H1" t="s">
-        <v>1353</v>
+        <v>1350</v>
       </c>
       <c r="I1" t="s">
-        <v>1318</v>
+        <v>1315</v>
       </c>
       <c r="J1" t="s">
-        <v>1354</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1355</v>
+        <v>1352</v>
       </c>
       <c r="B2" t="s">
-        <v>1333</v>
+        <v>1330</v>
       </c>
       <c r="C2" t="s">
         <v>1077</v>
@@ -7253,10 +7265,10 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1356</v>
+        <v>1353</v>
       </c>
       <c r="B3" t="s">
-        <v>1334</v>
+        <v>1331</v>
       </c>
       <c r="C3" t="s">
         <v>1077</v>
@@ -7270,10 +7282,10 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1357</v>
+        <v>1354</v>
       </c>
       <c r="B4" t="s">
-        <v>1336</v>
+        <v>1333</v>
       </c>
       <c r="C4" t="s">
         <v>1077</v>
@@ -7287,19 +7299,19 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1358</v>
+        <v>1355</v>
       </c>
       <c r="B5" t="s">
-        <v>1338</v>
+        <v>1335</v>
       </c>
       <c r="C5" t="s">
         <v>1097</v>
       </c>
       <c r="F5" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="G5" t="s">
-        <v>1340</v>
+        <v>1337</v>
       </c>
       <c r="H5" s="4">
         <v>0.40833333333333333</v>
@@ -7310,10 +7322,10 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1359</v>
+        <v>1356</v>
       </c>
       <c r="B6" t="s">
-        <v>1350</v>
+        <v>1347</v>
       </c>
       <c r="C6" t="s">
         <v>138</v>
@@ -7327,10 +7339,10 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1360</v>
+        <v>1357</v>
       </c>
       <c r="B7" t="s">
-        <v>1344</v>
+        <v>1341</v>
       </c>
       <c r="C7" t="s">
         <v>1077</v>
@@ -7344,10 +7356,10 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1361</v>
+        <v>1358</v>
       </c>
       <c r="B8" t="s">
-        <v>1346</v>
+        <v>1343</v>
       </c>
       <c r="C8" t="s">
         <v>1077</v>
@@ -7361,19 +7373,19 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1362</v>
+        <v>1359</v>
       </c>
       <c r="B9" t="s">
-        <v>1348</v>
+        <v>1345</v>
       </c>
       <c r="C9" t="s">
         <v>1097</v>
       </c>
       <c r="F9" t="s">
-        <v>1339</v>
+        <v>1336</v>
       </c>
       <c r="G9" t="s">
-        <v>1340</v>
+        <v>1337</v>
       </c>
       <c r="H9" s="4">
         <v>0.58750000000000002</v>
@@ -7384,10 +7396,10 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1363</v>
+        <v>1360</v>
       </c>
       <c r="B10" t="s">
-        <v>1364</v>
+        <v>1361</v>
       </c>
       <c r="C10" t="s">
         <v>138</v>
@@ -7401,10 +7413,10 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1365</v>
+        <v>1362</v>
       </c>
       <c r="B11" t="s">
-        <v>1352</v>
+        <v>1349</v>
       </c>
       <c r="C11" t="s">
         <v>1077</v>
@@ -13136,7 +13148,7 @@
   <sheetFormatPr defaultRowHeight="13.3" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.3828125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.61328125" customWidth="1"/>
+    <col min="2" max="2" width="52.4609375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.921875" customWidth="1"/>
     <col min="4" max="4" width="11.4609375" customWidth="1"/>
     <col min="5" max="6" width="30.07421875" customWidth="1"/>
@@ -13170,10 +13182,10 @@
         <v>1255</v>
       </c>
       <c r="I1" t="s">
-        <v>1368</v>
+        <v>1365</v>
       </c>
       <c r="J1" t="s">
-        <v>1369</v>
+        <v>1366</v>
       </c>
       <c r="K1" t="s">
         <v>1258</v>
@@ -13210,7 +13222,7 @@
         <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>1292</v>
+        <v>1380</v>
       </c>
       <c r="C3" t="s">
         <v>1284</v>
@@ -13231,7 +13243,7 @@
         <v>1350</v>
       </c>
       <c r="K3" t="s">
-        <v>1293</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -13239,7 +13251,7 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>1291</v>
+        <v>1381</v>
       </c>
       <c r="C4" t="s">
         <v>1284</v>
@@ -13260,7 +13272,7 @@
         <v>1350</v>
       </c>
       <c r="K4" t="s">
-        <v>1294</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -13268,7 +13280,7 @@
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>1295</v>
+        <v>1382</v>
       </c>
       <c r="C5" t="s">
         <v>1284</v>
@@ -13289,7 +13301,7 @@
         <v>1350</v>
       </c>
       <c r="K5" t="s">
-        <v>1296</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -13456,7 +13468,7 @@
         <v>1277</v>
       </c>
       <c r="B12" t="s">
-        <v>1382</v>
+        <v>1379</v>
       </c>
       <c r="C12" t="s">
         <v>1283</v>
@@ -13465,10 +13477,10 @@
         <v>60</v>
       </c>
       <c r="E12" t="s">
-        <v>1380</v>
+        <v>1377</v>
       </c>
       <c r="F12" t="s">
-        <v>1381</v>
+        <v>1378</v>
       </c>
       <c r="G12">
         <v>500</v>

--- a/統合版・2026年三陸鉄道周辺ダイヤ_4_2.xlsx
+++ b/統合版・2026年三陸鉄道周辺ダイヤ_4_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dnaka_cy7a7ax\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{662EE79B-5FA0-482B-821D-061A79A77B95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{489CB7CE-C5C0-44BC-85A1-EE77A8872399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="16371" yWindow="0" windowWidth="14915" windowHeight="11709" activeTab="2" xr2:uid="{3339B9FF-A08C-4853-B3B5-D870D1D967CF}"/>
     <workbookView minimized="1" xWindow="30223" yWindow="1851" windowWidth="4697" windowHeight="9103" activeTab="2" xr2:uid="{EECD383A-838A-41CD-8AB1-343EAFF88011}"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3081" uniqueCount="1383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3083" uniqueCount="1385">
   <si>
     <t>事業者</t>
   </si>
@@ -3841,19 +3841,6 @@
     <t>団体・割引料金</t>
   </si>
   <si>
-    <t>青の洞窟サッパ船</t>
-    <rPh sb="0" eb="1">
-      <t>アオ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ドウクツ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>フネ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>北山崎断崖クルーズ</t>
     <rPh sb="0" eb="5">
       <t>キタヤマザキダンガイ</t>
@@ -3869,25 +3856,6 @@
   </si>
   <si>
     <t>1名のみの時は、7600円</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>青の洞窟サッパ船乗り場</t>
-    <rPh sb="0" eb="1">
-      <t>アオ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ドウクツ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>フネ</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>ノ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>バ</t>
-    </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -4095,15 +4063,6 @@
   </si>
   <si>
     <t>宮古うみねこ丸便</t>
-  </si>
-  <si>
-    <t>出崎ふ頭発⇒湾内周遊⇒浄土ヶ浜下船</t>
-  </si>
-  <si>
-    <t>出崎ふ頭・浄土ヶ浜間のショートカット</t>
-  </si>
-  <si>
-    <t>発着地に戻る湾内クルーズ</t>
   </si>
   <si>
     <t>久慈駅_発</t>
@@ -4451,13 +4410,79 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>宮古うみねこ丸（片道移動（出崎ふ頭→浄土ヶ浜））</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>宮古うみねこ丸（全体周遊クルーズ（出崎ふ頭発））</t>
     <rPh sb="21" eb="22">
       <t>ハツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>青の洞窟さっぱ船</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>青の洞窟さっぱ船乗り場</t>
+    <rPh sb="8" eb="9">
+      <t>ノ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>バ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>宮古うみねこ丸（移動（出崎ふ頭→浄土ヶ浜））</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>バス停までの送迎時間（往復約20分）を含めて設定してください。</t>
+  </si>
+  <si>
+    <t>説明</t>
+    <rPh sb="0" eb="2">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>出崎ふ頭発⇒湾内周遊後に浄土ヶ浜下船</t>
+    <rPh sb="10" eb="11">
+      <t>ゴ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>出崎ふ頭発⇒浄土ヶ浜下船</t>
+    <rPh sb="4" eb="5">
+      <t>ハツ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>ゲセン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>出崎ふ頭発⇒湾内周遊⇒出崎ふ頭下船</t>
+    <rPh sb="0" eb="2">
+      <t>デサキ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>トウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ワンナイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>シュウユウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>デサキ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>トウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ゲセン</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -4948,13 +4973,13 @@
         <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="E4">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>1370</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -4974,7 +4999,7 @@
         <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>1370</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -4982,7 +5007,7 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="C6" t="s">
         <v>7</v>
@@ -4994,7 +5019,7 @@
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>1370</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -5002,19 +5027,19 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="C7" t="s">
-        <v>1256</v>
+        <v>1377</v>
       </c>
       <c r="D7" t="s">
-        <v>1260</v>
+        <v>1378</v>
       </c>
       <c r="E7">
         <v>5</v>
       </c>
       <c r="F7" t="s">
-        <v>1371</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -5025,16 +5050,16 @@
         <v>11</v>
       </c>
       <c r="C8" t="s">
-        <v>1256</v>
+        <v>1377</v>
       </c>
       <c r="D8" t="s">
-        <v>1260</v>
+        <v>1378</v>
       </c>
       <c r="E8">
         <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>1372</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -5045,16 +5070,16 @@
         <v>10</v>
       </c>
       <c r="C9" t="s">
-        <v>1256</v>
+        <v>1377</v>
       </c>
       <c r="D9" t="s">
-        <v>1260</v>
+        <v>1378</v>
       </c>
       <c r="E9">
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>1372</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -5074,7 +5099,7 @@
         <v>10</v>
       </c>
       <c r="F10" t="s">
-        <v>1373</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -5134,7 +5159,7 @@
         <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>1374</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -5208,13 +5233,13 @@
         <v>18</v>
       </c>
       <c r="D17" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="E17">
         <v>12</v>
       </c>
       <c r="F17" t="s">
-        <v>1375</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -5222,13 +5247,13 @@
         <v>34</v>
       </c>
       <c r="B18" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="C18" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="D18" t="s">
-        <v>1367</v>
+        <v>1362</v>
       </c>
       <c r="E18">
         <v>5</v>
@@ -5239,16 +5264,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="B19" t="s">
-        <v>1367</v>
+        <v>1362</v>
       </c>
       <c r="C19" t="s">
         <v>34</v>
       </c>
       <c r="D19" t="s">
-        <v>1368</v>
+        <v>1363</v>
       </c>
       <c r="E19">
         <v>10</v>
@@ -5262,13 +5287,13 @@
         <v>34</v>
       </c>
       <c r="B20" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="C20" t="s">
-        <v>1364</v>
+        <v>1359</v>
       </c>
       <c r="D20" t="s">
-        <v>1367</v>
+        <v>1362</v>
       </c>
       <c r="E20">
         <v>5</v>
@@ -5279,16 +5304,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>1364</v>
+        <v>1359</v>
       </c>
       <c r="B21" t="s">
-        <v>1367</v>
+        <v>1362</v>
       </c>
       <c r="C21" t="s">
         <v>34</v>
       </c>
       <c r="D21" t="s">
-        <v>1368</v>
+        <v>1363</v>
       </c>
       <c r="E21">
         <v>10</v>
@@ -5299,42 +5324,42 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="B22" t="s">
-        <v>1363</v>
+        <v>1358</v>
       </c>
       <c r="C22" t="s">
-        <v>1377</v>
+        <v>1372</v>
       </c>
       <c r="D22" t="s">
-        <v>1378</v>
+        <v>1373</v>
       </c>
       <c r="E22">
         <v>20</v>
       </c>
       <c r="F22" t="s">
-        <v>1376</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>1359</v>
+      </c>
+      <c r="B23" t="s">
         <v>1364</v>
       </c>
-      <c r="B23" t="s">
-        <v>1369</v>
-      </c>
       <c r="C23" t="s">
-        <v>1377</v>
+        <v>1372</v>
       </c>
       <c r="D23" t="s">
-        <v>1378</v>
+        <v>1373</v>
       </c>
       <c r="E23">
         <v>20</v>
       </c>
       <c r="F23" t="s">
-        <v>1376</v>
+        <v>1371</v>
       </c>
     </row>
   </sheetData>
@@ -5377,16 +5402,16 @@
         <v>55</v>
       </c>
       <c r="H1" t="s">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="I1" t="s">
+        <v>1285</v>
+      </c>
+      <c r="J1" t="s">
         <v>1287</v>
       </c>
-      <c r="J1" t="s">
-        <v>1289</v>
-      </c>
       <c r="K1" t="s">
-        <v>1286</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
@@ -6691,18 +6716,18 @@
         <v>55</v>
       </c>
       <c r="H1" t="s">
-        <v>1294</v>
+        <v>1289</v>
       </c>
       <c r="I1" t="s">
-        <v>1295</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1296</v>
+        <v>1291</v>
       </c>
       <c r="B2" t="s">
-        <v>1297</v>
+        <v>1292</v>
       </c>
       <c r="C2" t="s">
         <v>138</v>
@@ -6716,10 +6741,10 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1298</v>
+        <v>1293</v>
       </c>
       <c r="B3" t="s">
-        <v>1299</v>
+        <v>1294</v>
       </c>
       <c r="C3" t="s">
         <v>138</v>
@@ -6733,10 +6758,10 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1300</v>
+        <v>1295</v>
       </c>
       <c r="B4" t="s">
-        <v>1301</v>
+        <v>1296</v>
       </c>
       <c r="C4" t="s">
         <v>138</v>
@@ -6750,10 +6775,10 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1302</v>
+        <v>1297</v>
       </c>
       <c r="B5" t="s">
-        <v>1303</v>
+        <v>1298</v>
       </c>
       <c r="C5" t="s">
         <v>138</v>
@@ -6767,10 +6792,10 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1304</v>
+        <v>1299</v>
       </c>
       <c r="B6" t="s">
-        <v>1305</v>
+        <v>1300</v>
       </c>
       <c r="C6" t="s">
         <v>138</v>
@@ -6784,10 +6809,10 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1306</v>
+        <v>1301</v>
       </c>
       <c r="B7" t="s">
-        <v>1307</v>
+        <v>1302</v>
       </c>
       <c r="C7" t="s">
         <v>138</v>
@@ -6801,10 +6826,10 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1308</v>
+        <v>1303</v>
       </c>
       <c r="B8" t="s">
-        <v>1309</v>
+        <v>1304</v>
       </c>
       <c r="C8" t="s">
         <v>138</v>
@@ -6818,10 +6843,10 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1310</v>
+        <v>1305</v>
       </c>
       <c r="B9" t="s">
-        <v>1311</v>
+        <v>1306</v>
       </c>
       <c r="C9" t="s">
         <v>138</v>
@@ -6835,10 +6860,10 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1312</v>
+        <v>1307</v>
       </c>
       <c r="B10" t="s">
-        <v>1313</v>
+        <v>1308</v>
       </c>
       <c r="C10" t="s">
         <v>138</v>
@@ -6884,18 +6909,18 @@
         <v>55</v>
       </c>
       <c r="H1" t="s">
-        <v>1314</v>
+        <v>1309</v>
       </c>
       <c r="I1" t="s">
-        <v>1315</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1316</v>
+        <v>1311</v>
       </c>
       <c r="B2" t="s">
-        <v>1317</v>
+        <v>1312</v>
       </c>
       <c r="C2" t="s">
         <v>138</v>
@@ -6909,10 +6934,10 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1318</v>
+        <v>1313</v>
       </c>
       <c r="B3" t="s">
-        <v>1319</v>
+        <v>1314</v>
       </c>
       <c r="C3" t="s">
         <v>138</v>
@@ -6926,10 +6951,10 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1320</v>
+        <v>1315</v>
       </c>
       <c r="B4" t="s">
-        <v>1321</v>
+        <v>1316</v>
       </c>
       <c r="C4" t="s">
         <v>138</v>
@@ -6943,10 +6968,10 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1322</v>
+        <v>1317</v>
       </c>
       <c r="B5" t="s">
-        <v>1323</v>
+        <v>1318</v>
       </c>
       <c r="C5" t="s">
         <v>138</v>
@@ -6960,10 +6985,10 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1324</v>
+        <v>1319</v>
       </c>
       <c r="B6" t="s">
-        <v>1325</v>
+        <v>1320</v>
       </c>
       <c r="C6" t="s">
         <v>138</v>
@@ -6977,10 +7002,10 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1326</v>
+        <v>1321</v>
       </c>
       <c r="B7" t="s">
-        <v>1327</v>
+        <v>1322</v>
       </c>
       <c r="C7" t="s">
         <v>138</v>
@@ -7032,18 +7057,18 @@
         <v>55</v>
       </c>
       <c r="H1" t="s">
-        <v>1294</v>
+        <v>1289</v>
       </c>
       <c r="I1" t="s">
-        <v>1328</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1329</v>
+        <v>1324</v>
       </c>
       <c r="B2" t="s">
-        <v>1330</v>
+        <v>1325</v>
       </c>
       <c r="C2" t="s">
         <v>1077</v>
@@ -7057,10 +7082,10 @@
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1332</v>
+        <v>1327</v>
       </c>
       <c r="B3" t="s">
-        <v>1333</v>
+        <v>1328</v>
       </c>
       <c r="C3" t="s">
         <v>1077</v>
@@ -7074,19 +7099,19 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1334</v>
+        <v>1329</v>
       </c>
       <c r="B4" t="s">
-        <v>1335</v>
+        <v>1330</v>
       </c>
       <c r="C4" t="s">
         <v>1097</v>
       </c>
       <c r="F4" t="s">
-        <v>1336</v>
+        <v>1331</v>
       </c>
       <c r="G4" t="s">
-        <v>1337</v>
+        <v>1332</v>
       </c>
       <c r="H4" s="4">
         <v>0.39583333333333331</v>
@@ -7097,10 +7122,10 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1338</v>
+        <v>1333</v>
       </c>
       <c r="B5" t="s">
-        <v>1339</v>
+        <v>1334</v>
       </c>
       <c r="C5" t="s">
         <v>138</v>
@@ -7114,10 +7139,10 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1340</v>
+        <v>1335</v>
       </c>
       <c r="B6" t="s">
-        <v>1341</v>
+        <v>1336</v>
       </c>
       <c r="C6" t="s">
         <v>1077</v>
@@ -7131,10 +7156,10 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1342</v>
+        <v>1337</v>
       </c>
       <c r="B7" t="s">
-        <v>1343</v>
+        <v>1338</v>
       </c>
       <c r="C7" t="s">
         <v>1077</v>
@@ -7148,19 +7173,19 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1344</v>
+        <v>1339</v>
       </c>
       <c r="B8" t="s">
-        <v>1345</v>
+        <v>1340</v>
       </c>
       <c r="C8" t="s">
         <v>1097</v>
       </c>
       <c r="F8" t="s">
-        <v>1336</v>
+        <v>1331</v>
       </c>
       <c r="G8" t="s">
-        <v>1337</v>
+        <v>1332</v>
       </c>
       <c r="H8" s="4">
         <v>0.57847222222222228</v>
@@ -7171,10 +7196,10 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
       <c r="B9" t="s">
-        <v>1347</v>
+        <v>1342</v>
       </c>
       <c r="C9" t="s">
         <v>138</v>
@@ -7188,10 +7213,10 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1348</v>
+        <v>1343</v>
       </c>
       <c r="B10" t="s">
-        <v>1349</v>
+        <v>1344</v>
       </c>
       <c r="C10" t="s">
         <v>1077</v>
@@ -7237,21 +7262,21 @@
         <v>55</v>
       </c>
       <c r="H1" t="s">
-        <v>1350</v>
+        <v>1345</v>
       </c>
       <c r="I1" t="s">
-        <v>1315</v>
+        <v>1310</v>
       </c>
       <c r="J1" t="s">
-        <v>1351</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1352</v>
+        <v>1347</v>
       </c>
       <c r="B2" t="s">
-        <v>1330</v>
+        <v>1325</v>
       </c>
       <c r="C2" t="s">
         <v>1077</v>
@@ -7265,10 +7290,10 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1353</v>
+        <v>1348</v>
       </c>
       <c r="B3" t="s">
-        <v>1331</v>
+        <v>1326</v>
       </c>
       <c r="C3" t="s">
         <v>1077</v>
@@ -7282,10 +7307,10 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1354</v>
+        <v>1349</v>
       </c>
       <c r="B4" t="s">
-        <v>1333</v>
+        <v>1328</v>
       </c>
       <c r="C4" t="s">
         <v>1077</v>
@@ -7299,19 +7324,19 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1355</v>
+        <v>1350</v>
       </c>
       <c r="B5" t="s">
-        <v>1335</v>
+        <v>1330</v>
       </c>
       <c r="C5" t="s">
         <v>1097</v>
       </c>
       <c r="F5" t="s">
-        <v>1336</v>
+        <v>1331</v>
       </c>
       <c r="G5" t="s">
-        <v>1337</v>
+        <v>1332</v>
       </c>
       <c r="H5" s="4">
         <v>0.40833333333333333</v>
@@ -7322,10 +7347,10 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1356</v>
+        <v>1351</v>
       </c>
       <c r="B6" t="s">
-        <v>1347</v>
+        <v>1342</v>
       </c>
       <c r="C6" t="s">
         <v>138</v>
@@ -7339,10 +7364,10 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1357</v>
+        <v>1352</v>
       </c>
       <c r="B7" t="s">
-        <v>1341</v>
+        <v>1336</v>
       </c>
       <c r="C7" t="s">
         <v>1077</v>
@@ -7356,10 +7381,10 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1358</v>
+        <v>1353</v>
       </c>
       <c r="B8" t="s">
-        <v>1343</v>
+        <v>1338</v>
       </c>
       <c r="C8" t="s">
         <v>1077</v>
@@ -7373,19 +7398,19 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1359</v>
+        <v>1354</v>
       </c>
       <c r="B9" t="s">
-        <v>1345</v>
+        <v>1340</v>
       </c>
       <c r="C9" t="s">
         <v>1097</v>
       </c>
       <c r="F9" t="s">
-        <v>1336</v>
+        <v>1331</v>
       </c>
       <c r="G9" t="s">
-        <v>1337</v>
+        <v>1332</v>
       </c>
       <c r="H9" s="4">
         <v>0.58750000000000002</v>
@@ -7396,10 +7421,10 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1360</v>
+        <v>1355</v>
       </c>
       <c r="B10" t="s">
-        <v>1361</v>
+        <v>1356</v>
       </c>
       <c r="C10" t="s">
         <v>138</v>
@@ -7413,10 +7438,10 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1362</v>
+        <v>1357</v>
       </c>
       <c r="B11" t="s">
-        <v>1349</v>
+        <v>1344</v>
       </c>
       <c r="C11" t="s">
         <v>1077</v>
@@ -13144,7 +13169,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B9E270AA-17A2-4D2C-AEFB-5A166D0C1BBB}">
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr defaultRowHeight="13.3" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.3828125" bestFit="1" customWidth="1"/>
@@ -13156,24 +13181,24 @@
     <col min="9" max="10" width="14.53515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="B1" t="s">
         <v>1253</v>
       </c>
       <c r="C1" t="s">
-        <v>1281</v>
+        <v>1279</v>
       </c>
       <c r="D1" t="s">
-        <v>1282</v>
+        <v>1280</v>
       </c>
       <c r="E1" t="s">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="F1" t="s">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="G1" t="s">
         <v>1254</v>
@@ -13182,33 +13207,36 @@
         <v>1255</v>
       </c>
       <c r="I1" t="s">
-        <v>1365</v>
+        <v>1360</v>
       </c>
       <c r="J1" t="s">
-        <v>1366</v>
+        <v>1361</v>
       </c>
       <c r="K1" t="s">
-        <v>1258</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+        <v>1257</v>
+      </c>
+      <c r="L1" t="s">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="B2" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="C2" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="D2">
         <v>30</v>
       </c>
       <c r="E2" t="s">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="F2" t="s">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -13217,111 +13245,129 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>39</v>
       </c>
       <c r="B3" t="s">
-        <v>1380</v>
+        <v>1379</v>
       </c>
       <c r="C3" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="D3">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E3" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="F3" t="s">
         <v>13</v>
       </c>
       <c r="G3">
-        <v>1500</v>
+        <v>600</v>
       </c>
       <c r="H3">
         <v>1350</v>
       </c>
-      <c r="K3" t="s">
-        <v>1291</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I3">
+        <v>300</v>
+      </c>
+      <c r="J3">
+        <v>300</v>
+      </c>
+      <c r="L3" t="s">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>1381</v>
+        <v>1375</v>
       </c>
       <c r="C4" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="E4" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="F4" t="s">
         <v>13</v>
       </c>
       <c r="G4">
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="H4">
         <v>1350</v>
       </c>
-      <c r="K4" t="s">
-        <v>1292</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I4">
+        <v>900</v>
+      </c>
+      <c r="J4">
+        <v>680</v>
+      </c>
+      <c r="L4" t="s">
+        <v>1382</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>39</v>
       </c>
       <c r="B5" t="s">
-        <v>1382</v>
+        <v>1376</v>
       </c>
       <c r="C5" t="s">
-        <v>1284</v>
+        <v>1282</v>
       </c>
       <c r="D5">
         <v>60</v>
       </c>
       <c r="E5" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="F5" t="s">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="G5">
-        <v>1500</v>
+        <v>1800</v>
       </c>
       <c r="H5">
         <v>1350</v>
       </c>
-      <c r="K5" t="s">
-        <v>1293</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I5">
+        <v>900</v>
+      </c>
+      <c r="J5">
+        <v>680</v>
+      </c>
+      <c r="L5" t="s">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="B6" t="s">
-        <v>1256</v>
+        <v>1377</v>
       </c>
       <c r="C6" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="D6" s="2">
         <v>4.1666666666666664E-2</v>
       </c>
       <c r="E6" t="s">
-        <v>1256</v>
+        <v>1377</v>
       </c>
       <c r="F6" t="s">
-        <v>1260</v>
+        <v>1378</v>
       </c>
       <c r="G6">
         <v>2000</v>
@@ -13330,24 +13376,24 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="B7" t="s">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="C7" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="D7" s="2">
         <v>6.25E-2</v>
       </c>
       <c r="E7" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="F7" t="s">
-        <v>1275</v>
+        <v>1273</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -13356,24 +13402,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="B8" t="s">
         <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="D8" s="2">
         <v>4.1666666666666664E-2</v>
       </c>
       <c r="E8" t="s">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="F8" t="s">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="G8">
         <v>1100</v>
@@ -13382,24 +13428,24 @@
         <v>820</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="B9" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="C9" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="D9" s="2">
         <v>3.4722222222222224E-2</v>
       </c>
       <c r="E9" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="F9" t="s">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="G9">
         <v>2500</v>
@@ -13408,15 +13454,15 @@
         <v>2250</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="B10" t="s">
         <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>1285</v>
+        <v>1283</v>
       </c>
       <c r="D10" s="2">
         <v>5.5555555555555552E-2</v>
@@ -13434,18 +13480,18 @@
         <v>3800</v>
       </c>
       <c r="K10" t="s">
-        <v>1259</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1280</v>
+        <v>1278</v>
       </c>
       <c r="B11" t="s">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="C11" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="D11">
         <v>30</v>
@@ -13454,7 +13500,7 @@
         <v>43</v>
       </c>
       <c r="F11" t="s">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -13463,24 +13509,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="B12" t="s">
-        <v>1379</v>
+        <v>1374</v>
       </c>
       <c r="C12" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="D12">
         <v>60</v>
       </c>
       <c r="E12" t="s">
-        <v>1377</v>
+        <v>1372</v>
       </c>
       <c r="F12" t="s">
-        <v>1378</v>
+        <v>1373</v>
       </c>
       <c r="G12">
         <v>500</v>
@@ -13494,25 +13540,28 @@
       <c r="J12">
         <v>150</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L12" t="s">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="B13" t="s">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="C13" t="s">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="D13" s="2">
         <v>6.25E-2</v>
       </c>
       <c r="E13" t="s">
-        <v>1276</v>
+        <v>1274</v>
       </c>
       <c r="F13" t="s">
-        <v>1277</v>
+        <v>1275</v>
       </c>
       <c r="G13">
         <v>0</v>

--- a/統合版・2026年三陸鉄道周辺ダイヤ_4_2.xlsx
+++ b/統合版・2026年三陸鉄道周辺ダイヤ_4_2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dnaka_cy7a7ax\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{489CB7CE-C5C0-44BC-85A1-EE77A8872399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECFFF069-D369-486B-8833-DE0295919386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16371" yWindow="0" windowWidth="14915" windowHeight="11709" activeTab="2" xr2:uid="{3339B9FF-A08C-4853-B3B5-D870D1D967CF}"/>
+    <workbookView xWindow="16354" yWindow="-103" windowWidth="29692" windowHeight="11829" activeTab="2" xr2:uid="{3339B9FF-A08C-4853-B3B5-D870D1D967CF}"/>
     <workbookView minimized="1" xWindow="30223" yWindow="1851" windowWidth="4697" windowHeight="9103" activeTab="2" xr2:uid="{EECD383A-838A-41CD-8AB1-343EAFF88011}"/>
   </bookViews>
   <sheets>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3083" uniqueCount="1385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3084" uniqueCount="1386">
   <si>
     <t>事業者</t>
   </si>
@@ -4483,6 +4483,28 @@
     </rPh>
     <rPh sb="15" eb="17">
       <t>ゲセン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>順番待ちの時間も含めて50分以上で設定してください。</t>
+    <rPh sb="0" eb="3">
+      <t>ジュンバンマ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>フク</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>フン</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>イジョウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>セッテイ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -13375,6 +13397,9 @@
       <c r="H6">
         <v>2000</v>
       </c>
+      <c r="L6" t="s">
+        <v>1385</v>
+      </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">

--- a/統合版・2026年三陸鉄道周辺ダイヤ_4_2.xlsx
+++ b/統合版・2026年三陸鉄道周辺ダイヤ_4_2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dnaka_cy7a7ax\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECFFF069-D369-486B-8833-DE0295919386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EA4F7D1-89E2-43A6-8F04-C7ABADB1DC49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16354" yWindow="-103" windowWidth="29692" windowHeight="11829" activeTab="2" xr2:uid="{3339B9FF-A08C-4853-B3B5-D870D1D967CF}"/>
+    <workbookView xWindow="16371" yWindow="0" windowWidth="14915" windowHeight="11709" activeTab="2" xr2:uid="{3339B9FF-A08C-4853-B3B5-D870D1D967CF}"/>
     <workbookView minimized="1" xWindow="30223" yWindow="1851" windowWidth="4697" windowHeight="9103" activeTab="2" xr2:uid="{EECD383A-838A-41CD-8AB1-343EAFF88011}"/>
   </bookViews>
   <sheets>
@@ -13290,7 +13290,7 @@
         <v>600</v>
       </c>
       <c r="H3">
-        <v>1350</v>
+        <v>600</v>
       </c>
       <c r="I3">
         <v>300</v>

--- a/統合版・2026年三陸鉄道周辺ダイヤ_4_2.xlsx
+++ b/統合版・2026年三陸鉄道周辺ダイヤ_4_2.xlsx
@@ -8,10 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dnaka_cy7a7ax\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29459E36-BA8A-419C-8C50-7BC938D4A7D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62DEDE68-2673-4624-86BE-A47D259919E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16371" yWindow="0" windowWidth="14915" windowHeight="11709" firstSheet="13" activeTab="14" xr2:uid="{3339B9FF-A08C-4853-B3B5-D870D1D967CF}"/>
-    <workbookView xWindow="31114" yWindow="0" windowWidth="14915" windowHeight="11709" activeTab="1" xr2:uid="{EECD383A-838A-41CD-8AB1-343EAFF88011}"/>
+    <workbookView xWindow="16371" yWindow="0" windowWidth="14915" windowHeight="11709" activeTab="1" xr2:uid="{3339B9FF-A08C-4853-B3B5-D870D1D967CF}"/>
+    <workbookView minimized="1" xWindow="27129" yWindow="3000" windowWidth="4697" windowHeight="9103" activeTab="1" xr2:uid="{EECD383A-838A-41CD-8AB1-343EAFF88011}"/>
   </bookViews>
   <sheets>
     <sheet name="乗換設定" sheetId="1" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3149" uniqueCount="1416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3154" uniqueCount="1418">
   <si>
     <t>事業者</t>
   </si>
@@ -4832,6 +4832,16 @@
       <t>オナ</t>
     </rPh>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>乗車定員</t>
+    <rPh sb="0" eb="4">
+      <t>ジョウシャテイイン</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>4人まで1台</t>
   </si>
 </sst>
 </file>
@@ -8557,16 +8567,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="13.3"/>
   <cols>
     <col min="1" max="1" width="30.07421875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.4609375" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="23.53515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.84375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -8586,13 +8597,16 @@
         <v>1357</v>
       </c>
       <c r="G1" t="s">
+        <v>1416</v>
+      </c>
+      <c r="H1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -8612,7 +8626,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -8632,7 +8646,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -8652,7 +8666,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:9">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -8672,7 +8686,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -8692,7 +8706,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:9">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -8712,7 +8726,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -8731,11 +8745,11 @@
       <c r="F8">
         <v>300</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:9">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -8754,11 +8768,11 @@
       <c r="F9">
         <v>600</v>
       </c>
-      <c r="G9" t="s">
+      <c r="H9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:9">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -8777,11 +8791,11 @@
       <c r="F10">
         <v>900</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <v>1350</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -8800,11 +8814,11 @@
       <c r="F11">
         <v>900</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <v>1350</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:9">
       <c r="A12" t="s">
         <v>1245</v>
       </c>
@@ -8824,7 +8838,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:9">
       <c r="A13" t="s">
         <v>40</v>
       </c>
@@ -8844,10 +8858,13 @@
         <v>0</v>
       </c>
       <c r="G13" t="s">
+        <v>1417</v>
+      </c>
+      <c r="H13" t="s">
         <v>1415</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:9">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -8867,10 +8884,13 @@
         <v>0</v>
       </c>
       <c r="G14" t="s">
+        <v>1417</v>
+      </c>
+      <c r="H14" t="s">
         <v>1415</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:9">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -8890,10 +8910,13 @@
         <v>0</v>
       </c>
       <c r="G15" t="s">
+        <v>1417</v>
+      </c>
+      <c r="H15" t="s">
         <v>1415</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:9">
       <c r="A16" t="s">
         <v>40</v>
       </c>
@@ -8913,6 +8936,9 @@
         <v>0</v>
       </c>
       <c r="G16" t="s">
+        <v>1417</v>
+      </c>
+      <c r="H16" t="s">
         <v>1415</v>
       </c>
     </row>
